--- a/docs/ops/チケット棚卸し案_2026-05-02.xlsx
+++ b/docs/ops/チケット棚卸し案_2026-05-02.xlsx
@@ -7,17 +7,23 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_UserReview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_AllTickets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Consolidation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_CloseCandidates" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Hearing" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Rules" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Hearing_Round2" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Hearing_Round3" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Hearing_Round4_5" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Hearing_Round6_Final" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Cost_Principle" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Final_JP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_ACTIVE_Detail" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_KEEP_Detail" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_HOLD_OBSOLETE" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Rules_Detail" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Claude_Prompt" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_UserReview" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_AllTickets" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Consolidation" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_CloseCandidates" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Hearing" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Rules" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Hearing_Round2" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Hearing_Round3" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Hearing_Round4_5" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Hearing_Round6_Final" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Cost_Principle" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -88,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -109,6 +115,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -474,215 +483,130 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="86" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
-      <c r="C1" s="7" t="inlineStr">
-        <is>
-          <t>????</t>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>本日決めたこと</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>詳細</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ACTIVE??</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BUG-003 / BUG-004+291</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>WP status mutation audit ? silent skip/????/??????/?????????2??</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>今日の結論</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVEは最大2件だけ</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>BUG-003 と BUG-004+291 を次に現場Claudeへ渡す。他のP1候補は一括ACTIVE化しない。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>?????</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>229 / 282 / 293</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>?????282 flag ON?293 FULL_EXERCISE??</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>最優先の事故防止</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>公開状態と候補消失</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>公開状態が勝手に変わる疑い、候補が見えずに消える問題、YOSHILOVER対象外メールが来る問題を最優先で見る。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>??????</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>234 / 247 / 250 / 256 / 254 / 283</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>???postgame strict?farm_result?lineup?quote????</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>品質方針</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>ハルシネーション防止</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>AI/Codexに足りない数字・勝敗・選手名を書かせない。source/meta由来の事実だけでテンプレに入れる。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>??????</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>277-280 / 290</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>??????????????????????????/???</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>コスト方針</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Geminiを呼ばない設計</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>品質改善と同時にGemini追加呼び出し、再生成、メール増加を抑える。まずregex/marker/template/slot-fillで対処する。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>??????</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>??????????????????????????</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>マーケ方針</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>巨人専門価値</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>二軍・若手・復帰組・スタメンを追える、のもとけ型の巨人専門サイトに寄せる。ただしsource追加は後。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>front/MKT</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>245 / 195/197 / 246</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>???????????????X????????????????</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>HOLD/???</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>230? / 248 / 255 / 260 / 288</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>runtime cost???????source?????</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>OBSOLETE??</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>238 / 252 / 274 / 296</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>??draft-only?X??????Gmail filter?codex-shadow redesign??????</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CI??</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>299? / 201 / 275</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>???299?????201/275???/close???</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Final hearing</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Round6????</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>295?comment?postgame??????/?????????????291?publishable??OK???????292?ledger/log?????????????</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Cost principle</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>????</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>????????Gemini?????/??????/????????????????????source/meta??????template/regex/slot-fill???</t>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>運用方針</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>userは貼るだけ</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>userは違和感や現場報告をチャットに貼るだけ。CodexがBUG_INBOXへ整理し、ClaudeがACTIVE最大2件を進める。</t>
         </is>
       </c>
     </row>
@@ -692,6 +616,1129 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>candidate</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>close check</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>DONE維持</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>完了済み。履歴だけ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>DONE候補</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>frontに自動投稿が出なければclose。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>DONE候補</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>codex-shadow-trigger pause済みならclose。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>195/197</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>DONE候補</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>記事下Xシェア導線がliveならclose。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>OBSOLETE候補</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Gmail filter。CI根本対応ではない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>OBSOLETE候補</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>GPTs手動運用で優先低。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>優先</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>聞きたいこと</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>なぜ必要か</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>user回答形式</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>user回答</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>反映案</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>245: 画面上に「自動投稿」カテゴリはまだ見えるか</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>見えなければDONE候補にできる</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>見える / 見えない / 不明</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>見える</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>245はDONE不可。front表示修正としてKEEP/次候補。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>297: codex-shadow-trigger はもう止めた前提でよいか</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>pause済みならDONE候補にできる</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>止めたはず / 不明</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>止めた</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>297はread-onlyでpause確認できればDONE候補。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>252/274 は不要寄りとしてOBSOLETE候補でよいか</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>X手動GPTs・Gmail filterで優先度が低い</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>OK / HOLD</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>不要</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>252/274はOBSOLETE候補。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>275: GitHub Actions赤は今も気にするか</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>赤ならKEEP、緑ならDONE候補</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>気にする / 後で / 不明</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>エラー出てない</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>275はCI緑をread-only確認できればDONE候補。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>251 SEO/noindex はHOLD深めでよいか</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>触るとSEO影響が大きい</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>OK / HOLD</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>HOLD深め</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>251はHOLD深め。ACTIVEに上げない。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ルール</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>確定前提</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>このExcelは棚卸し案。user確認後に反映。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>最大2件。現場に一括投入しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>OBSOLETE</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>削除ではない。履歴を残して現場ACTIVEから外す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>evidenceありのみ。deploy済みだけではDONEにしない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>作業停止ではない。read-only/doc-only/evidenceは可。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>user作業</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>最終確認のみ。ticket番号や優先度分類はしない。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ticket/group</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>user回答</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>反映案</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>195 / 197</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>完全にはできてない</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>KEEP。front/manual X share導線の残作業候補。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>246-MKT</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>やりたい</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>KEEP。観戦ガイド本線。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>248 / 255 / 260</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>後回し</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>HOLD。マーケ拡張・コメントbadge・独自記事型は後段。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>277 / 278 / 279 / 280</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>必要</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>KEEP/統合候補。タイトル/通知/summary品質系として整理。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>やりたい</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>KEEP。二軍記事増やす系。ただしsource/公開影響に注意。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>後で</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>HOLD。source追加は今やらない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>必要</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>KEEP。weak title rescueは残す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>気になる</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>KEEP。subtype誤分類は残す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>いらない</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>OBSOLETE候補。codex-shadow再設計は不要。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>後で</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>HOLD。夜間draft-only/朝レポートは後段。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SEOはいじらない。もうできてる</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>DONE/OBSOLETE候補。ACTIVEに上げない。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>ticket/group</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>user??</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>229 / 282 / 293</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Gemini?????????????</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>KEEP?????????282 flag ON?293 FULL_EXERCISE??</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>230 / 230A / 230A1 / 230D</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>HOLD?????????????</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>234 / 247 / 250 / 256</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>KEEP???????/strict?????</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>KEEP????????????????/?????</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>??cleanup???????????????</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>??cleanup????????????229/235/300/BUG-004????</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>KEEP???????/regression contract????</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>????????????????????publish??????YOSHILOVER?????????</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BUG-004?????P1???publish??/????/???source???audit?</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>body_contract_validate fail??????</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ledger/log?????????????BUG-004???????????</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>299 / 201 / 275</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>pytest/CI/flaky?????</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>299??????201/275???/close???</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>210 / 210b / 210e</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>288????OK</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>source expansion??288????</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="47" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>ticket/group</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>user??</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>291 / BUG-004</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>YOSHILOVER??????????????</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>???source?mail??????error????????</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>???????publish????????OK????PUBLISH?????</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ACTIVE?read-only audit?publishable/review/hold/mail?????????</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>277-280</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>???????????????????????</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>???????clarty-first????????????????????</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>???????????????????????????</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>??/??/????YOSHILOVER???????KEEP?</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>??postgame?????????????</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>postgame strict??starter stats????fact????</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>250 / 256</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>??????????????????????/??/Twitter??????</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>quote???????????cross-source duplicate??????</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>????????????????front????????</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>KEEP/?front???</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>195 / 197</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>???X????????</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>KEEP?????????????</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>246-MKT</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>?????????????????</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>???MVP????????????</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BUG_INBOX</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>???????Codex???ticket?????OK</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>user??????Codex???/???</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>??draft-only / ?????????</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>OBSOLETE???</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>230?</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GCP runtime cost????Artifact Registry????????</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>HOLD??????????????cleanup?????????</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ACTIVE??</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BUG-003 / BUG-004+291?OK</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>??2????</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -812,7 +1859,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -915,6 +1962,1278 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="56" customWidth="1" min="5" max="5"/>
+    <col width="74" customWidth="1" min="6" max="6"/>
+    <col width="74" customWidth="1" min="7" max="7"/>
+    <col width="56" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>チケット名</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>優先度</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>扱い</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>なぜ重要か</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>次にやること</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>close条件</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>禁止/注意</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>BUG-003</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>WP status mutation audit</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>P1候補</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE候補 1</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>公開状態が勝手に変わった疑い。publish済み記事がdraft/private/pending等に戻る事故があると、サイトの公開復旧・信頼性に直結する。</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>直近24〜72hのWP status変化、WP REST更新ログ、guarded-publish/publish-notice周辺のstatus更新pathをread-onlyで確認する。既存publishをdraft/privateへ戻す処理が存在しない、または十分guardされていることを確認する。</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>問題なしを証拠付きで確認できた、または原因を特定して修正・verifyできた場合のみDONE。証拠なしはDONE禁止でP1_REVIEWまたはOBSERVE継続。</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>本番変更なし。deploy/env/flag/Scheduler/SEO/source/Gemini/mail変更禁止。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>BUG-004 + 291</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>silent skip / 候補消失 / YOSHILOVER対象外メール / 自動公開判定整理</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>P1候補</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE候補 2</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>候補が生成されたのにpublish/review/hold/skip/errorのどれにも見えず消える問題、またYOSHILOVER対象外sourceのメールが来る問題。userが監視できない事故源。</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>候補の終端状態をread-onlyで確認する。publishable判定OKだけ自動公開、review/hold/対象外はメール抑制または別扱い。YOSHILOVER対象外sourceメールは完全に送らない方針。mail対象ならpublish判定へ戻すが、現状は判定境界が曖昧なのでまず整理する。</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>直近runでunaccounted candidateが0、skip/hold/review理由がlog/ledger/state rowに残る、YOSHILOVER対象外メールが出ない経路が確認できる。証拠なしDONE禁止。</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>292のbody_contract failは通常メール不要。ledger/logで件数確認できればよい。メール大量化させない。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="86" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>テーマ</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>扱い</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>詳しい理由</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>次の扱い</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>229 / 282 / 293</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Gemini費用削減本線</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Gemini費用削減はまだ本線。282は293のFULL_EXERCISE_OK後に進める。preflight gate、skip visible化、重複抑制を中心に、Geminiを呼ばない設計へ寄せる。</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>293のexercise evidence確認、282 flag ONはuser判断境界。コスト削減と候補可視化を両立する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>234 / 247 / 250 / 256</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>本文テンプレ・strict系</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>ハルシネーション対策の本線。優先順は postgame strict → farm_result → lineup → 監督/選手コメント。コメント系は全文がなくても一部引用ならよいが、重複通知を抑える。</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>source/meta由来のslot-fillとbody validatorで守る。自由作文で補完させない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>postgame strict</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>一軍試合後記事では、特に先発投手成績を守る。勝敗・スコア・投手成績の誤りはブランド毀損が大きい。</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>先発投手成績、勝敗、得点場面、スコアをsource/meta由来に限定。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>投手回数・スターター表記正規化</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>数字・投手成績のハルシネーション防止に直結。1/3回、2/3回、先発/リリーフ表記の誤読を防ぐ。</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>numeric guard / baseball fact consistencyへ吸収または連動。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>今後の重複記事削減</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>ABSORB</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>過去重複記事cleanupは不要。ただし今後の重複記事を減らすのは急ぎ。</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>229 / 235 / 300 / BUG-004へ吸収。cleanup mutationはしない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>277 / 278 / 279 / 280</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>タイトル・RTタイトル・メール件名・summary改善</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>最優先は「何の記事かわからない」タイトルの解消。SEOや煽りより、読者が一瞬で内容を理解できることを優先。</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>まずタイトルclarityを改善。メール件名/summaryは後続。SEOは後で対策。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>二軍・若手・復帰組を増やす</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>YOSHILOVERの差別化軸。大手が出さない巨人専門情報、のもとけ型の価値。最初は復帰組と二軍スタメンを重視。</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>source追加は後。まず既存source/既存テンプレで増やせる範囲を確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>独自記事要件・regression contract</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>独自記事や観戦ガイドへ広げる前に、どの品質条件を満たすべきかを契約化する。</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>実装前にregression contractとして保持。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>weak title rescue</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>弱いタイトル救済は必要。ただし自動修正より検知優先。</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>弱いタイトルを検知し、候補化/review化してから段階的に修正。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>subtype誤分類防止</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>KEEP / P1候補</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>ハルシネーション防止で重要。最優先はcomment系がpostgame扱いになる事故。加えて勝敗・スコア・試合結果factの誤分類も防ぐ。</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>234/247と連動し、template_key判定はconfidence highのみ。判定不能はdefault/review。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>release composition gate</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>止めているticketのコードや作業ゴミがbuild/deployに混ざる事故を防ぐ親ticket。</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>deploy前にcommit range、HOLD ticket混入、rollback target 3種を確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>195 / 197</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>記事下Xシェア導線</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>読者向けの手動Xシェア導線は必要。X APIや自動投稿ではなく、読者が共有しやすい導線。</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>front改善候補として保持。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>自動投稿カテゴリ非表示</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>KEEP / 次front候補</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>画面上に「自動投稿」カテゴリがまだ見える。読者に内部カテゴリが見えるのは不自然。</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>次front候補。表示修正・確認を行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>246-MKT</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>今日の巨人ファン観戦ガイド</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>トップページで今日見る順番が分かる観戦ガイド。記事一覧ではなく、試合前後の導線を作る。</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>まずトップページだけ。記事下展開は後。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>299 / 201 / 275</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>pytest / CI / flaky整理</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>KEEP親 / 吸収</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>pytest/CI/flaky整理は必要。299を親にし、201と275は吸収/close候補。GitHub Actions赤は現状出ていない。</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>299でbaseline/new failure/out-of-scopeの表現を統一。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="92" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>テーマ</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>扱い</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>230 / 230A / 230A1 / 230D</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>GCP runtime cost / scheduler cadence / overlap audit</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>後で。安全な小額cleanupは候補として残すが、今の主線ではない。Artifact Registry等は安全なら検討。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>night draft-only / morning report</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>OBSOLETE候補</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>user回答で捨てる。夜間draft-only/朝レポートは今後の主線から外す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>248 / 255 / 260</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>マーケ拡張・コメントbadge・独自記事型</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>後回し。246-MKT観戦ガイドが先。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SEO/noindex戦略</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>DONE/OBSOLETE候補</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>SEOはいじらない。もうできている。今後ACTIVEに上げない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>X自動化/関連施策</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>OBSOLETE候補</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>X文面はGPTsで作るため不要寄り。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Gmail filter</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>OBSOLETE候補</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Gmail通知仕分けは不要。GitHub Actions赤の根本対応でもない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>288 / 210 / 210b / 210e</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>source expansion系</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>HOLD / 288へ吸収</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>source追加・取得元拡張は後で。210系は288に吸収。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>codex-shadow redesign</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>OBSOLETE候補</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>codex-shadow再設計は不要。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="112" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>ルール</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>チケット番号</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>振り直し禁止。既存番号は履歴として残し、必要ならalias/吸収先を付ける。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE数</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>最大2件。今はBUG-003とBUG-004+291。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>user入力</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>userはチャットに違和感や現場報告を貼るだけ。Excel編集や優先度分類はしない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Codex役割</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>貼られた報告をBUG_INBOXへ反映し、既存ticketへ吸収し、ACTIVE候補を最大2件に圧縮する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Claude役割</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>現場管理。ACTIVE最大2件を実行管理し、Codex A/Bへdispatchする。正常系の長い報告はしない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>コスト横串</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Gemini追加呼び出しを増やさない。重複再生成を減らす。メール通知を増やさない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ハルシネーション対策</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>数字・勝敗・選手名・投手成績はsource/meta由来に限定。足りないものをAIに書かせない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>292通知</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>body_contract failは通常メール不要。ledger/logで件数確認できればよい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>291通知</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>YOSHILOVER対象外sourceメールは完全に送らない。mail対象ならpublish判定へ戻すが、境界はread-only auditで確認。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>DONE条件</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>evidenceがあるものだけDONE。証拠なしはP1_REVIEW/OBSERVE継続。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="122" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>現場Claudeへ渡す1文</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>BUG_INBOX初回棚卸しでは、ACTIVE候補は BUG-003 WP status mutation audit と BUG-004+291 silent skip / 候補消失 / YOSHILOVER対象外メール / 自動公開判定整理の2件だけです。他のP1候補は一括ACTIVE化しないでください。291は対象外sourceメールを完全に送らない方針、mail対象ならpublish判定へ戻す方針ですが、publish判定境界が曖昧なのでまずread-only auditで確認してください。292は通常メール不要、ledger/log確認に寄せてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>禁止</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>新規deploy、env/flag変更、Scheduler変更、SEO変更、source追加、Gemini call増加、mail通知増加はこの棚卸し作業ではしない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>報告してよいもの</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE完了、P1相当の異常、rollback必要、USER_DECISION_REQUIRED、新たにP0/P1へ昇格すべき証拠。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>報告しないもの</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>cycle silent、異常なし定期報告、次wake予定、monitorなし、HOLD/OBSERVE/DONEの正常報告、長いlog貼り付け。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ACTIVE??</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BUG-003 / BUG-004+291</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>WP status mutation audit ? silent skip/????/??????/?????????2??</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>?????</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>229 / 282 / 293</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>?????282 flag ON?293 FULL_EXERCISE??</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>234 / 247 / 250 / 256 / 254 / 283</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>???postgame strict?farm_result?lineup?quote????</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>277-280 / 290</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>??????????????????????????/???</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>??????????????????????????</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>front/MKT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>245 / 195/197 / 246</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>???????????????X????????????????</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HOLD/???</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>230? / 248 / 255 / 260 / 288</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>runtime cost???????source?????</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>OBSOLETE??</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>238 / 252 / 274 / 296</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>??draft-only?X??????Gmail filter?codex-shadow redesign??????</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CI??</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>299? / 201 / 275</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>???299?????201/275???/close???</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Final hearing</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Round6????</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>295?comment?postgame??????/?????????????291?publishable??OK???????292?ledger/log?????????????</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Cost principle</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>????????Gemini?????/??????/????????????????????source/meta??????template/regex/slot-fill???</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4117,7 +6436,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4289,1127 +6608,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>candidate</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>close check</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>DONE維持</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>完了済み。履歴だけ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>DONE候補</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>frontに自動投稿が出なければclose。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>DONE候補</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>codex-shadow-trigger pause済みならclose。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>195/197</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>DONE候補</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>記事下Xシェア導線がliveならclose。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>OBSOLETE候補</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Gmail filter。CI根本対応ではない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>OBSOLETE候補</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>GPTs手動運用で優先低。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>優先</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>聞きたいこと</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>なぜ必要か</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>user回答形式</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>user回答</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>反映案</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>245: 画面上に「自動投稿」カテゴリはまだ見えるか</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>見えなければDONE候補にできる</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>見える / 見えない / 不明</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>見える</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>245はDONE不可。front表示修正としてKEEP/次候補。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>297: codex-shadow-trigger はもう止めた前提でよいか</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>pause済みならDONE候補にできる</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>止めたはず / 不明</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>止めた</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>297はread-onlyでpause確認できればDONE候補。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>252/274 は不要寄りとしてOBSOLETE候補でよいか</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>X手動GPTs・Gmail filterで優先度が低い</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>OK / HOLD</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>不要</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>252/274はOBSOLETE候補。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>275: GitHub Actions赤は今も気にするか</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>赤ならKEEP、緑ならDONE候補</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>気にする / 後で / 不明</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>エラー出てない</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>275はCI緑をread-only確認できればDONE候補。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>251 SEO/noindex はHOLD深めでよいか</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>触るとSEO影響が大きい</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>OK / HOLD</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>HOLD深め</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>251はHOLD深め。ACTIVEに上げない。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>項目</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ルール</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>確定前提</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>このExcelは棚卸し案。user確認後に反映。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>最大2件。現場に一括投入しない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>OBSOLETE</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>削除ではない。履歴を残して現場ACTIVEから外す。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>evidenceありのみ。deploy済みだけではDONEにしない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>作業停止ではない。read-only/doc-only/evidenceは可。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>user作業</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>最終確認のみ。ticket番号や優先度分類はしない。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ticket/group</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>user回答</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>反映案</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>195 / 197</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>完全にはできてない</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>KEEP。front/manual X share導線の残作業候補。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>246-MKT</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>やりたい</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>KEEP。観戦ガイド本線。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>248 / 255 / 260</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>後回し</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>HOLD。マーケ拡張・コメントbadge・独自記事型は後段。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>277 / 278 / 279 / 280</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>必要</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>KEEP/統合候補。タイトル/通知/summary品質系として整理。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>やりたい</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>KEEP。二軍記事増やす系。ただしsource/公開影響に注意。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>後で</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>HOLD。source追加は今やらない。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>必要</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>KEEP。weak title rescueは残す。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>295</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>気になる</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>KEEP。subtype誤分類は残す。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>いらない</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>OBSOLETE候補。codex-shadow再設計は不要。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>後で</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>HOLD。夜間draft-only/朝レポートは後段。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>SEOはいじらない。もうできてる</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>DONE/OBSOLETE候補。ACTIVEに上げない。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>ticket/group</t>
-        </is>
-      </c>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t>user??</t>
-        </is>
-      </c>
-      <c r="C1" s="7" t="inlineStr">
-        <is>
-          <t>???</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>229 / 282 / 293</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Gemini?????????????</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>KEEP?????????282 flag ON?293 FULL_EXERCISE??</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>230 / 230A / 230A1 / 230D</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>HOLD?????????????</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>234 / 247 / 250 / 256</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>KEEP???????/strict?????</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>KEEP????????????????/?????</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>??cleanup???????????????</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>??cleanup????????????229/235/300/BUG-004????</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>??</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>KEEP???????/regression contract????</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>????????????????????publish??????YOSHILOVER?????????</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>BUG-004?????P1???publish??/????/???source???audit?</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>body_contract_validate fail??????</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ledger/log?????????????BUG-004???????????</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>299 / 201 / 275</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>pytest/CI/flaky?????</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>299??????201/275???/close???</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>210 / 210b / 210e</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>288????OK</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>source expansion??288????</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>ticket/group</t>
-        </is>
-      </c>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t>user??</t>
-        </is>
-      </c>
-      <c r="C1" s="7" t="inlineStr">
-        <is>
-          <t>???</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>291 / BUG-004</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>YOSHILOVER??????????????</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>???source?mail??????error????????</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>???????publish????????OK????PUBLISH?????</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ACTIVE?read-only audit?publishable/review/hold/mail?????????</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>277-280</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>???????????????????????</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>???????clarty-first????????????????????</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>???????????????????????????</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>??/??/????YOSHILOVER???????KEEP?</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>??postgame?????????????</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>postgame strict??starter stats????fact????</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>250 / 256</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>??????????????????????/??/Twitter??????</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>quote???????????cross-source duplicate??????</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>????????????????front????????</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>KEEP/?front???</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>195 / 197</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>???X????????</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>KEEP?????????????</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>246-MKT</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>?????????????????</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>???MVP????????????</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>BUG_INBOX</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>???????Codex???ticket?????OK</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>user??????Codex???/???</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>??draft-only / ?????????</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>OBSOLETE???</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>230?</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>GCP runtime cost????Artifact Registry????????</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>HOLD??????????????cleanup?????????</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>ACTIVE??</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>BUG-003 / BUG-004+291?OK</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>??2????</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/ops/チケット棚卸し案_2026-05-02.xlsx
+++ b/docs/ops/チケット棚卸し案_2026-05-02.xlsx
@@ -13,17 +13,18 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_HOLD_OBSOLETE" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Rules_Detail" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Claude_Prompt" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_UserReview" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_AllTickets" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Consolidation" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_CloseCandidates" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Hearing" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Rules" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Hearing_Round2" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Hearing_Round3" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Hearing_Round4_5" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Hearing_Round6_Final" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Cost_Principle" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_NewCandidate_GCP_Codex" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_UserReview" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_AllTickets" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Consolidation" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_CloseCandidates" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Hearing" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Rules" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Hearing_Round2" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Hearing_Round3" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Hearing_Round4_5" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Hearing_Round6_Final" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Cost_Principle" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -610,12 +611,203 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>次ACTIVE候補</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GCP Codex WP本文修正プレビュー v0</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>本文品質を早く見るためのpreview-only候補。Gemini原則0、WP本文変更なし。BUG-004+291後、またはBUG-003と入れ替え検討。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>親/分類</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>吸収候補</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>理由</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>扱い</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>294-PROCESS</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>BUG-005 / BUG-006 / BUG-007 / BUG-009</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>deploy混入・dirty・rollbackはrelease hygieneで一体管理</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>統合</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>293-COST / 229</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>BUG-010〜014</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Gemini費用雪崩・cache・prompt/capはcost governorで一体管理</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>統合</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>BUG-004 / 289 / 291 / 292</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>silent skip / 候補消失</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>userに見えない終端状態をまとめて見る</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>統合</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>234 / 247 / 277〜280</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>本文・タイトル・summary品質</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>品質系が分散。親を決めて吸収</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>統合候補</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>246-MKT</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>248-MKT-* / 255-MKT / 260-MKT</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>マーケ導線・観戦ガイド・独自記事型を分けすぎない</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>統合候補</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>X/GPTs手動方針</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>252 / MKT系X候補</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>X自動化しないため低優先</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>HOLD/OBSOLETE候補</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -753,7 +945,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -955,7 +1147,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1057,7 +1249,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1275,7 +1467,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1481,7 +1673,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1738,7 +1930,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1859,7 +2051,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1967,7 +2159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2103,6 +2295,48 @@
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>292のbody_contract failは通常メール不要。ledger/logで件数確認できればよい。メール大量化させない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NEW_CANDIDATE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GCP Codex WP本文修正プレビュー v0</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>P1候補/次ACTIVE候補</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>まだACTIVEではないが早めにやりたい</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>本文品質を早く見たい。preview-onlyならデグレリスクを抑えてGCP Codexの実力を確認できる。</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>postgameまたはfarm_result少数で、元本文と修正文候補を比較できるartifactを出す。</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>WP本文変更なし、publish変更なし、Gemini原則0で品質確認できる。</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>本番本文を書き換えない。自由作文させない。</t>
         </is>
       </c>
     </row>
@@ -3016,6 +3250,216 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>候補名</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>GCP Codex WP本文修正プレビュー v0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>扱い</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>NEW_CANDIDATE。ただしuser希望により次ACTIVE候補へ昇格可能。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>目的</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>WordPress本文をいきなり変更せず、GCP Codexで修正文候補だけ作り、userが早く品質を確認できるようにする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>なぜ重要か</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>本文品質が運用負担の中心。完全自動化前に、GCP Codexがどの程度安全に本文を直せるか早く見たい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>対象</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>まず postgame または farm_result の少数。最初から全subtypeに広げない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>必須制約</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>preview-only / WP本文変更なし / publish状態変更なし / env/flag/Scheduler/SEO/source変更なし。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>コスト制約</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Gemini call原則0。使う場合は別判断・上限付き。まずGCP Codex/deterministic template/source-meta slot-fillで行う。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>本文修正方針</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>自由作文ではなく、source/metaにある数字・勝敗・選手名・投手成績だけをテンプレに入れる。足りない事実は補完しない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>やってよい修正</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>placeholder削除、空見出し削除、sourceにないoptional section削除、短文化、タイトルと本文の整合確認、元本文/修正文diff生成。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>やってはいけない修正</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>sourceにない数字/選手名/勝敗/コメントの補完、X投稿文生成、長文再作文、Gemini追加呼び出し前提の修正。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>出力</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>元本文、修正文候補、変更理由、削ったsection、source/meta由来fact一覧、危険/不明点をledgerまたはreview artifactへ出す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>close条件</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>userが元本文と修正文候補を比較できる。数字・勝敗・選手名のハルシネーションなし。費用増なし、または小さい。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ACTIVE化条件</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>BUG-004+291の整理後、または本文品質確認を優先する場合に、BUG-003と入れ替えてACTIVE候補へ昇格可能。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>関連ticket</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>247 postgame strict / 234 template contract / 295 subtype誤分類 / 290 weak title rescue / 254 numeric normalization</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>現場Claudeへ渡す時の注意</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>いきなり本番本文を書き換えない。preview-onlyで品質を見る。Gemini制限を明記。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3233,7 +3677,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6434,178 +6878,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>親/分類</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>吸収候補</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>理由</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>扱い</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>294-PROCESS</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>BUG-005 / BUG-006 / BUG-007 / BUG-009</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>deploy混入・dirty・rollbackはrelease hygieneで一体管理</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>統合</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>293-COST / 229</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>BUG-010〜014</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Gemini費用雪崩・cache・prompt/capはcost governorで一体管理</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>統合</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>BUG-004 / 289 / 291 / 292</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>silent skip / 候補消失</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>userに見えない終端状態をまとめて見る</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>統合</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>234 / 247 / 277〜280</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>本文・タイトル・summary品質</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>品質系が分散。親を決めて吸収</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>統合候補</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>246-MKT</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>248-MKT-* / 255-MKT / 260-MKT</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>マーケ導線・観戦ガイド・独自記事型を分けすぎない</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>統合候補</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>X/GPTs手動方針</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>252 / MKT系X候補</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>X自動化しないため低優先</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>HOLD/OBSOLETE候補</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/ops/チケット棚卸し案_2026-05-02.xlsx
+++ b/docs/ops/チケット棚卸し案_2026-05-02.xlsx
@@ -25,8 +25,29 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Hearing_Round4_5" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Hearing_Round6_Final" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Cost_Principle" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Publish0_NarrowUnlock" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'00_Final_JP'!$A$1:$C$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_ACTIVE_Detail'!$A$1:$H$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_KEEP_Detail'!$A$1:$E$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_HOLD_OBSOLETE'!$A$1:$D$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_Rules_Detail'!$A$1:$B$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_Claude_Prompt'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_NewCandidate_GCP_Codex'!$A$1:$B$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'00_UserReview'!$A$1:$C$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'01_AllTickets'!$A$1:$K$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'02_Consolidation'!$A$1:$D$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'03_CloseCandidates'!$A$1:$C$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'04_Hearing'!$A$1:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'05_Rules'!$A$1:$B$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'06_Hearing_Round2'!$A$1:$C$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'07_Hearing_Round3'!$A$1:$C$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'08_Hearing_Round4_5'!$A$1:$C$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'09_Hearing_Round6_Final'!$A$1:$C$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'10_Cost_Principle'!$A$1:$B$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'07_Publish0_NarrowUnlock'!$A$1:$B$7</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -83,7 +104,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -91,11 +112,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -118,6 +153,24 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -487,148 +540,149 @@
   <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="86" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>本日決めたこと</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>詳細</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>今日の結論</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>ACTIVEは最大2件だけ</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>BUG-003 と BUG-004+291 を次に現場Claudeへ渡す。他のP1候補は一括ACTIVE化しない。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>最優先の事故防止</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>公開状態と候補消失</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>公開状態が勝手に変わる疑い、候補が見えずに消える問題、YOSHILOVER対象外メールが来る問題を最優先で見る。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>品質方針</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>ハルシネーション防止</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>AI/Codexに足りない数字・勝敗・選手名を書かせない。source/meta由来の事実だけでテンプレに入れる。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>コスト方針</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Geminiを呼ばない設計</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>品質改善と同時にGemini追加呼び出し、再生成、メール増加を抑える。まずregex/marker/template/slot-fillで対処する。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>マーケ方針</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>巨人専門価値</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>二軍・若手・復帰組・スタメンを追える、のもとけ型の巨人専門サイトに寄せる。ただしsource追加は後。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>運用方針</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>userは貼るだけ</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>userは違和感や現場報告をチャットに貼るだけ。CodexがBUG_INBOXへ整理し、ClaudeがACTIVE最大2件を進める。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>次ACTIVE候補</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>GCP Codex WP本文修正プレビュー v0</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>本文品質を早く見るためのpreview-only候補。Gemini原則0、WP本文変更なし。BUG-004+291後、またはBUG-003と入れ替え検討。</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -649,160 +703,161 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>親/分類</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>吸収候補</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>理由</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>扱い</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>294-PROCESS</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>BUG-005 / BUG-006 / BUG-007 / BUG-009</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>deploy混入・dirty・rollbackはrelease hygieneで一体管理</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>統合</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>293-COST / 229</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>BUG-010〜014</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>Gemini費用雪崩・cache・prompt/capはcost governorで一体管理</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>統合</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>BUG-004 / 289 / 291 / 292</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>silent skip / 候補消失</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>userに見えない終端状態をまとめて見る</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>統合</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>234 / 247 / 277〜280</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>本文・タイトル・summary品質</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>品質系が分散。親を決めて吸収</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>統合候補</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>246-MKT</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>248-MKT-* / 255-MKT / 260-MKT</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>マーケ導線・観戦ガイド・独自記事型を分けすぎない</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>統合候補</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>X/GPTs手動方針</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>252 / MKT系X候補</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>X自動化しないため低優先</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>HOLD/OBSOLETE候補</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -816,131 +871,132 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>candidate</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>close check</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>240</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>DONE維持</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>完了済み。履歴だけ。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>245</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>DONE候補</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>frontに自動投稿が出なければclose。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>297</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>DONE候補</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>codex-shadow-trigger pause済みならclose。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>195/197</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>DONE候補</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>記事下Xシェア導線がliveならclose。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>274</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>OBSOLETE候補</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Gmail filter。CI根本対応ではない。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>252</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>OBSOLETE候補</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>GPTs手動運用で優先低。</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -954,195 +1010,198 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>優先</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>聞きたいこと</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>なぜ必要か</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>user回答形式</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>user回答</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>反映案</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>245: 画面上に「自動投稿」カテゴリはまだ見えるか</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>見えなければDONE候補にできる</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>見える / 見えない / 不明</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>見える</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>245はDONE不可。front表示修正としてKEEP/次候補。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>297: codex-shadow-trigger はもう止めた前提でよいか</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>pause済みならDONE候補にできる</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>止めたはず / 不明</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>止めた</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>297はread-onlyでpause確認できればDONE候補。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>252/274 は不要寄りとしてOBSOLETE候補でよいか</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>X手動GPTs・Gmail filterで優先度が低い</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>OK / HOLD</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>不要</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>252/274はOBSOLETE候補。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>275: GitHub Actions赤は今も気にするか</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>赤ならKEEP、緑ならDONE候補</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>気にする / 後で / 不明</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>エラー出てない</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>275はCI緑をread-only確認できればDONE候補。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>251 SEO/noindex はHOLD深めでよいか</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>触るとSEO影響が大きい</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>OK / HOLD</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>HOLD深め</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>251はHOLD深め。ACTIVEに上げない。</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1156,95 +1215,96 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="41" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>ルール</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>確定前提</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>このExcelは棚卸し案。user確認後に反映。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>最大2件。現場に一括投入しない。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>OBSOLETE</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>削除ではない。履歴を残して現場ACTIVEから外す。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>evidenceありのみ。deploy済みだけではDONEにしない。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>作業停止ではない。read-only/doc-only/evidenceは可。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>user作業</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>最終確認のみ。ticket番号や優先度分類はしない。</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1257,212 +1317,218 @@
   </sheetPr>
   <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>ticket/group</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>user回答</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>反映案</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>195 / 197</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>完全にはできてない</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>KEEP。front/manual X share導線の残作業候補。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>246-MKT</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>やりたい</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>KEEP。観戦ガイド本線。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>248 / 255 / 260</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>後回し</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>HOLD。マーケ拡張・コメントbadge・独自記事型は後段。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>277 / 278 / 279 / 280</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>必要</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>KEEP/統合候補。タイトル/通知/summary品質系として整理。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>やりたい</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>KEEP。二軍記事増やす系。ただしsource/公開影響に注意。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>後で</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>HOLD。source追加は今やらない。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>290</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>必要</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>KEEP。weak title rescueは残す。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>295</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>気になる</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>KEEP。subtype誤分類は残す。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>296</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>いらない</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>OBSOLETE候補。codex-shadow再設計は不要。</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>238</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>後で</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>HOLD。夜間draft-only/朝レポートは後段。</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>251</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>SEOはいじらない。もうできてる</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>DONE/OBSOLETE候補。ACTIVEに上げない。</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1477,198 +1543,199 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>ticket/group</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>user??</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>???</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>229 / 282 / 293</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>Gemini?????????????</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>KEEP?????????282 flag ON?293 FULL_EXERCISE??</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>230 / 230A / 230A1 / 230D</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>??</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>HOLD?????????????</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>234 / 247 / 250 / 256</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>??</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>KEEP???????/strict?????</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>??</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>KEEP????????????????/?????</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>264</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>??cleanup???????????????</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>??cleanup????????????229/235/300/BUG-004????</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>283</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>??</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>KEEP???????/regression contract????</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>291</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>????????????????????publish??????YOSHILOVER?????????</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>BUG-004?????P1???publish??/????/???source???audit?</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>292</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>body_contract_validate fail??????</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>ledger/log?????????????BUG-004???????????</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>299 / 201 / 275</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>pytest/CI/flaky?????</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>299??????201/275???/close???</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>210 / 210b / 210e</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>288????OK</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>source expansion??288????</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1684,248 +1751,249 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>ticket/group</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>user??</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>???</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>291 / BUG-004</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>YOSHILOVER??????????????</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>???source?mail??????error????????</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>291</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>???????publish????????OK????PUBLISH?????</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>ACTIVE?read-only audit?publishable/review/hold/mail?????????</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>277-280</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>???????????????????????</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>???????clarty-first????????????????????</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>???????????????????????????</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>??/??/????YOSHILOVER???????KEEP?</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>247</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>??postgame?????????????</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>postgame strict??starter stats????fact????</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>250 / 256</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>??????????????????????/??/Twitter??????</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>quote???????????cross-source duplicate??????</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>245</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>????????????????front????????</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>KEEP/?front???</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>195 / 197</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>???X????????</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>KEEP?????????????</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>246-MKT</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>?????????????????</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>???MVP????????????</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>BUG_INBOX</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>???????Codex???ticket?????OK</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>user??????Codex???/???</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>238</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>??draft-only / ?????????</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>OBSOLETE???</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>230?</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>GCP runtime cost????Artifact Registry????????</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>HOLD??????????????cleanup?????????</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>ACTIVE??</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>BUG-003 / BUG-004+291?OK</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>??2????</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1940,113 +2008,114 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>ticket/group</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>user??</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>???</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>295 subtype???</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>comment??postgame???????????????????fact?????????????</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>KEEP?GCP?Codex repair??????????source/meta???slot-fill?numeric guard????</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>291 ??????</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>??????=??publish?????publishable??OK???????review/hold/????????????????</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>ACTIVE BUG-004+291?read-only audit?publishable/review/hold/mail??????????</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>292 body_contract fail</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>?????????ledger/log?????????????????????</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>BUG-004????????????????????</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>277-280 ??????</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>??????????????????SEO??????</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>????clarity-first?</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>??????</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>CODEX_APP_TICKET_VIEW.md ? ????????_2026-05-02.xlsx ?commit OK?</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>???????commit???</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2060,95 +2129,199 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>rule</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Gemini????????????</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>????/regex/marker/source slot-fill??????</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>???????</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>source_url_hash/content_hash/dedupe/preflight gate????</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>??????????source/meta??</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>LLM/Codex??????????????review/????</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>??????????</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>fail/review/hold????????????292?ledger/log???</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>YOSHILOVER????????</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>291????source mail??????</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>???????????</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>SEO???????????????????</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>BUG-004+291 ?ACTIVE?????????ticket?????</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>publish=0??????????????????publish path????</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>????</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>277 title quality / 289 post_gen_validate / 290 weak title rescue?? / 4-tier strict / duplicate / backlog / freshness / body_contract / subtype??? / numeric guard / placeholder / source facts??</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>publish??????????</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>YOSHILOVER???source_url???subtype/template_key high confidence?numeric guard pass?body_contract pass?placeholder???silent skip???title???????????????review/hold????</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>??????</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>publish gate??????????????????????noindex???review threshold???????mail???user?????SEO??</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>??Claude?????</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>BUG-004+291 ??? publish=0???? + narrow publish-path unlock ????????????ticket????read-only?????????????????????publish path?????????????</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2162,185 +2335,186 @@
   <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="56" customWidth="1" min="5" max="5"/>
-    <col width="74" customWidth="1" min="6" max="6"/>
-    <col width="74" customWidth="1" min="7" max="7"/>
-    <col width="56" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>チケット名</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>優先度</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>扱い</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>なぜ重要か</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>次にやること</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>close条件</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>禁止/注意</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>BUG-003</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>WP status mutation audit</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>P1候補</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>ACTIVE候補 1</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>公開状態が勝手に変わった疑い。publish済み記事がdraft/private/pending等に戻る事故があると、サイトの公開復旧・信頼性に直結する。</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>直近24〜72hのWP status変化、WP REST更新ログ、guarded-publish/publish-notice周辺のstatus更新pathをread-onlyで確認する。既存publishをdraft/privateへ戻す処理が存在しない、または十分guardされていることを確認する。</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>問題なしを証拠付きで確認できた、または原因を特定して修正・verifyできた場合のみDONE。証拠なしはDONE禁止でP1_REVIEWまたはOBSERVE継続。</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="10" t="inlineStr">
         <is>
           <t>本番変更なし。deploy/env/flag/Scheduler/SEO/source/Gemini/mail変更禁止。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>BUG-004 + 291</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>silent skip / 候補消失 / YOSHILOVER対象外メール / 自動公開判定整理</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>silent skip / ???? / YOSHILOVER?????? / ???????? / publish=0????</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>P1候補</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>ACTIVE候補 2</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>候補が生成されたのにpublish/review/hold/skip/errorのどれにも見えず消える問題、またYOSHILOVER対象外sourceのメールが来る問題。userが監視できない事故源。</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>候補の終端状態をread-onlyで確認する。publishable判定OKだけ自動公開、review/hold/対象外はメール抑制または別扱い。YOSHILOVER対象外sourceメールは完全に送らない方針。mail対象ならpublish判定へ戻すが、現状は判定境界が曖昧なのでまず整理する。</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>直近runでunaccounted candidateが0、skip/hold/review理由がlog/ledger/state rowに残る、YOSHILOVER対象外メールが出ない経路が確認できる。証拠なしDONE禁止。</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>292のbody_contract failは通常メール不要。ledger/logで件数確認できればよい。メール大量化させない。</t>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>??????????publish/review/hold/skip/error??????????????YOSHILOVER???source??????????publish=0??????user?????????????????????????</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>????????read-only??????publish=0???277 title quality?289 post_gen_validate?290 weak title rescue???4-tier strict?duplicate/backlog/freshness?body_contract?subtype????numeric guard?placeholder?source facts??????????????????????????????publish path???narrow unlock??????</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>??run?unaccounted candidate?0?skip/hold/review???log/ledger/state row????YOSHILOVER????????????????(YOSHILOVER???source_url?subtype/template_key high confidence?numeric/body pass?placeholder???title???review/hold????)????????publish???????????DONE???</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>publish gate??????????noindex???review threshold???????mail??????292 body_contract fail?????????ledger/log????????????</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>NEW_CANDIDATE</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>GCP Codex WP本文修正プレビュー v0</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>P1候補/次ACTIVE候補</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>まだACTIVEではないが早めにやりたい</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>本文品質を早く見たい。preview-onlyならデグレリスクを抑えてGCP Codexの実力を確認できる。</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>postgameまたはfarm_result少数で、元本文と修正文候補を比較できるartifactを出す。</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>WP本文変更なし、publish変更なし、Gemini原則0で品質確認できる。</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>本番本文を書き換えない。自由作文させない。</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2354,446 +2528,447 @@
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="86" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>テーマ</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>扱い</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>詳しい理由</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>次の扱い</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>229 / 282 / 293</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>Gemini費用削減本線</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>Gemini費用削減はまだ本線。282は293のFULL_EXERCISE_OK後に進める。preflight gate、skip visible化、重複抑制を中心に、Geminiを呼ばない設計へ寄せる。</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>293のexercise evidence確認、282 flag ONはuser判断境界。コスト削減と候補可視化を両立する。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>234 / 247 / 250 / 256</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>本文テンプレ・strict系</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>ハルシネーション対策の本線。優先順は postgame strict → farm_result → lineup → 監督/選手コメント。コメント系は全文がなくても一部引用ならよいが、重複通知を抑える。</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>source/meta由来のslot-fillとbody validatorで守る。自由作文で補完させない。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>247</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>postgame strict</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>一軍試合後記事では、特に先発投手成績を守る。勝敗・スコア・投手成績の誤りはブランド毀損が大きい。</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>先発投手成績、勝敗、得点場面、スコアをsource/meta由来に限定。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>投手回数・スターター表記正規化</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>数字・投手成績のハルシネーション防止に直結。1/3回、2/3回、先発/リリーフ表記の誤読を防ぐ。</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>numeric guard / baseball fact consistencyへ吸収または連動。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>264</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>今後の重複記事削減</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>ABSORB</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>過去重複記事cleanupは不要。ただし今後の重複記事を減らすのは急ぎ。</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>229 / 235 / 300 / BUG-004へ吸収。cleanup mutationはしない。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>277 / 278 / 279 / 280</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>タイトル・RTタイトル・メール件名・summary改善</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>最優先は「何の記事かわからない」タイトルの解消。SEOや煽りより、読者が一瞬で内容を理解できることを優先。</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>まずタイトルclarityを改善。メール件名/summaryは後続。SEOは後で対策。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>二軍・若手・復帰組を増やす</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>YOSHILOVERの差別化軸。大手が出さない巨人専門情報、のもとけ型の価値。最初は復帰組と二軍スタメンを重視。</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>source追加は後。まず既存source/既存テンプレで増やせる範囲を確認。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>283</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>独自記事要件・regression contract</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>独自記事や観戦ガイドへ広げる前に、どの品質条件を満たすべきかを契約化する。</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>実装前にregression contractとして保持。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>290</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>weak title rescue</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>弱いタイトル救済は必要。ただし自動修正より検知優先。</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>弱いタイトルを検知し、候補化/review化してから段階的に修正。</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>295</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>subtype誤分類防止</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>KEEP / P1候補</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>ハルシネーション防止で重要。最優先はcomment系がpostgame扱いになる事故。加えて勝敗・スコア・試合結果factの誤分類も防ぐ。</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>234/247と連動し、template_key判定はconfidence highのみ。判定不能はdefault/review。</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>294</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>release composition gate</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>止めているticketのコードや作業ゴミがbuild/deployに混ざる事故を防ぐ親ticket。</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>deploy前にcommit range、HOLD ticket混入、rollback target 3種を確認する。</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>195 / 197</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>記事下Xシェア導線</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>読者向けの手動Xシェア導線は必要。X APIや自動投稿ではなく、読者が共有しやすい導線。</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>front改善候補として保持。</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>245</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>自動投稿カテゴリ非表示</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>KEEP / 次front候補</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>画面上に「自動投稿」カテゴリがまだ見える。読者に内部カテゴリが見えるのは不自然。</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>次front候補。表示修正・確認を行う。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>246-MKT</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>今日の巨人ファン観戦ガイド</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>トップページで今日見る順番が分かる観戦ガイド。記事一覧ではなく、試合前後の導線を作る。</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>まずトップページだけ。記事下展開は後。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>299 / 201 / 275</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>pytest / CI / flaky整理</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>KEEP親 / 吸収</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>pytest/CI/flaky整理は必要。299を親にし、201と275は吸収/close候補。GitHub Actions赤は現状出ていない。</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>299でbaseline/new failure/out-of-scopeの表現を統一。</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2807,211 +2982,212 @@
   <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="92" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>テーマ</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>扱い</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>理由</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>230 / 230A / 230A1 / 230D</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>GCP runtime cost / scheduler cadence / overlap audit</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>後で。安全な小額cleanupは候補として残すが、今の主線ではない。Artifact Registry等は安全なら検討。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>238</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>night draft-only / morning report</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>OBSOLETE候補</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>user回答で捨てる。夜間draft-only/朝レポートは今後の主線から外す。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>248 / 255 / 260</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>マーケ拡張・コメントbadge・独自記事型</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>後回し。246-MKT観戦ガイドが先。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>251</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>SEO/noindex戦略</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>DONE/OBSOLETE候補</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>SEOはいじらない。もうできている。今後ACTIVEに上げない。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>252</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>X自動化/関連施策</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>OBSOLETE候補</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>X文面はGPTsで作るため不要寄り。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>274</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Gmail filter</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>OBSOLETE候補</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>Gmail通知仕分けは不要。GitHub Actions赤の根本対応でもない。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>288 / 210 / 210b / 210e</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>source expansion系</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>HOLD / 288へ吸収</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>source追加・取得元拡張は後で。210系は288に吸収。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>296</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>codex-shadow redesign</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>OBSOLETE候補</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>codex-shadow再設計は不要。</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3025,143 +3201,144 @@
   <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="112" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>ルール</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>チケット番号</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>振り直し禁止。既存番号は履歴として残し、必要ならalias/吸収先を付ける。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>ACTIVE数</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>最大2件。今はBUG-003とBUG-004+291。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>user入力</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>userはチャットに違和感や現場報告を貼るだけ。Excel編集や優先度分類はしない。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Codex役割</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>貼られた報告をBUG_INBOXへ反映し、既存ticketへ吸収し、ACTIVE候補を最大2件に圧縮する。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Claude役割</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>現場管理。ACTIVE最大2件を実行管理し、Codex A/Bへdispatchする。正常系の長い報告はしない。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>コスト横串</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Gemini追加呼び出しを増やさない。重複再生成を減らす。メール通知を増やさない。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>ハルシネーション対策</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>数字・勝敗・選手名・投手成績はsource/meta由来に限定。足りないものをAIに書かせない。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>292通知</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>body_contract failは通常メール不要。ledger/logで件数確認できればよい。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>291通知</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>YOSHILOVER対象外sourceメールは完全に送らない。mail対象ならpublish判定へ戻すが、境界はread-only auditで確認。</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>DONE条件</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>evidenceがあるものだけDONE。証拠なしはP1_REVIEW/OBSERVE継続。</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3172,74 +3349,87 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="122" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>現場Claudeへ渡す1文</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>BUG_INBOX初回棚卸しでは、ACTIVE候補は BUG-003 WP status mutation audit と BUG-004+291 silent skip / 候補消失 / YOSHILOVER対象外メール / 自動公開判定整理の2件だけです。他のP1候補は一括ACTIVE化しないでください。291は対象外sourceメールを完全に送らない方針、mail対象ならpublish判定へ戻す方針ですが、publish判定境界が曖昧なのでまずread-only auditで確認してください。292は通常メール不要、ledger/log確認に寄せてください。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>禁止</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>新規deploy、env/flag変更、Scheduler変更、SEO変更、source追加、Gemini call増加、mail通知増加はこの棚卸し作業ではしない。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>報告してよいもの</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>ACTIVE完了、P1相当の異常、rollback必要、USER_DECISION_REQUIRED、新たにP0/P1へ昇格すべき証拠。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>報告しないもの</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>cycle silent、異常なし定期報告、次wake予定、monitorなし、HOLD/OBSERVE/DONEの正常報告、長いlog貼り付け。</t>
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>?????????</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>BUG-004+291 ??? publish=0???? + narrow publish-path unlock ????????????ticket?????????????publish gate?????????????????????read-only??????????????????publish path?????????????????: 277 title quality?289 post_gen_validate?290 weak title rescue???4-tier??strict?duplicate/backlog/freshness?body_contract?subtype misclassify?numeric guard?placeholder?source facts???publish??????????: YOSHILOVER???source_url???subtype/template_key high confidence?numeric guard pass?body_contract pass?placeholder???silent skip???title?????????????review/hold???????????: publish gate??????????????????????noindex???review threshold???????mail???user?????SEO?????trigger????????narrow unlock?????P1???rollback???USER_DECISION_REQUIRED??????????????</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:B6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3253,203 +3443,204 @@
   <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>候補名</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>GCP Codex WP本文修正プレビュー v0</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>扱い</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>NEW_CANDIDATE。ただしuser希望により次ACTIVE候補へ昇格可能。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>目的</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>WordPress本文をいきなり変更せず、GCP Codexで修正文候補だけ作り、userが早く品質を確認できるようにする。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>なぜ重要か</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>本文品質が運用負担の中心。完全自動化前に、GCP Codexがどの程度安全に本文を直せるか早く見たい。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>対象</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>まず postgame または farm_result の少数。最初から全subtypeに広げない。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>必須制約</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>preview-only / WP本文変更なし / publish状態変更なし / env/flag/Scheduler/SEO/source変更なし。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>コスト制約</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Gemini call原則0。使う場合は別判断・上限付き。まずGCP Codex/deterministic template/source-meta slot-fillで行う。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>本文修正方針</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>自由作文ではなく、source/metaにある数字・勝敗・選手名・投手成績だけをテンプレに入れる。足りない事実は補完しない。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>やってよい修正</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>placeholder削除、空見出し削除、sourceにないoptional section削除、短文化、タイトルと本文の整合確認、元本文/修正文diff生成。</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>やってはいけない修正</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>sourceにない数字/選手名/勝敗/コメントの補完、X投稿文生成、長文再作文、Gemini追加呼び出し前提の修正。</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>出力</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>元本文、修正文候補、変更理由、削ったsection、source/meta由来fact一覧、危険/不明点をledgerまたはreview artifactへ出す。</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>close条件</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>userが元本文と修正文候補を比較できる。数字・勝敗・選手名のハルシネーションなし。費用増なし、または小さい。</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>ACTIVE化条件</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>BUG-004+291の整理後、または本文品質確認を優先する場合に、BUG-003と入れ替えてACTIVE候補へ昇格可能。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>関連ticket</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>247 postgame strict / 234 template contract / 295 subtype誤分類 / 290 weak title rescue / 254 numeric normalization</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>現場Claudeへ渡す時の注意</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>いきなり本番本文を書き換えない。preview-onlyで品質を見る。Gemini制限を明記。</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:B16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3463,216 +3654,217 @@
   <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>??</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>??</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>????</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>ACTIVE??</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>BUG-003 / BUG-004+291</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>WP status mutation audit ? silent skip/????/??????/?????????2??</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>?????</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>229 / 282 / 293</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>?????282 flag ON?293 FULL_EXERCISE??</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>??????</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>234 / 247 / 250 / 256 / 254 / 283</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>???postgame strict?farm_result?lineup?quote????</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>??????</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>277-280 / 290</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>??????????????????????????/???</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>??????</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>??????????????????????????</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>front/MKT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>245 / 195/197 / 246</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>???????????????X????????????????</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>HOLD/???</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>230? / 248 / 255 / 260 / 288</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>runtime cost???????source?????</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>OBSOLETE??</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>238 / 252 / 274 / 296</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>??draft-only?X??????Gmail filter?codex-shadow redesign??????</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>CI??</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>299? / 201 / 275</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>???299?????201/275???/close???</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Final hearing</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Round6????</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>295?comment?postgame??????/?????????????291?publishable??OK???????292?ledger/log?????????????</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Cost principle</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>????</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>????????Gemini?????/??????/????????????????????source/meta??????template/regex/slot-fill???</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3686,3196 +3878,3197 @@
   <dimension ref="A1:K56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="53" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="56" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="59" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="31" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>num</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>ticket</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>folder</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>priority</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>proposed_bucket</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>next_action</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>user_review</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>path</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>229</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>229-gemini-cost-governor-and-llm-call-reduction</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>doc/active</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>REVIEW_NEEDED</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>P0.5</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>229 Gemini cost governor + LLM call reduction</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>KEEP?</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="11" t="inlineStr">
         <is>
           <t>Gemini????????229/282/293?????</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="11" t="inlineStr">
         <is>
           <t>282?293 FULL_EXERCISE?</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" s="11" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="11" t="inlineStr">
         <is>
           <t>doc/active/229-gemini-cost-governor-and-llm-call-reduction.md</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>245</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>245-front-hide-auto-post-category-label</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="12" t="inlineStr">
         <is>
           <t>doc/active</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="12" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="12" t="inlineStr">
         <is>
           <t>P0.5</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="12" t="inlineStr">
         <is>
           <t>245 front hide internal auto-post category label</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>KEEP/次front候補</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="12" t="inlineStr">
         <is>
           <t>user確認: 画面上に「自動投稿」がまだ見える。DONE不可。</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="12" t="inlineStr">
         <is>
           <t>front表示修正またはdeploy/表示確認へ</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="K3" s="12" t="inlineStr">
         <is>
           <t>doc/active/245-front-hide-auto-post-category-label.md</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>246</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>246</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>doc/active</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>viral topic detection (SNS バズ検出 → 既存 subtype routing、dry-run)</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="13" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="13" t="inlineStr">
         <is>
           <t>user回答: 今日の巨人ファン観戦ガイドはやりたい。</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="13" t="inlineStr">
         <is>
           <t>MKT本線として保持</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K4" s="13" t="inlineStr">
         <is>
           <t>doc/active/246-viral-topic-detection.md</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>247</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>247-QA</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>doc/active</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="11" t="inlineStr">
         <is>
           <t>P0.5</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="11" t="inlineStr">
         <is>
           <t>postgame strict slot-fill POC(LLM 自由作文 → JSON 抽出 + 固定 template に slot-fill、type 別 block 振り分け)</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="11" t="inlineStr">
         <is>
           <t>??????/strict????????postgame strict?farm_result?lineup?quote?</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="11" t="inlineStr">
         <is>
           <t>???????????</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="11" t="inlineStr">
         <is>
           <t>doc/active/247-QA-postgame-strict-slot-fill-poc.md</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>248</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>248-MKT-2</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>doc/active</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>single 記事下部「この試合の関連記事」(同 game 導線、PHP front-only narrow)</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>user回答: マーケ拡張は後回し。</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t>246後</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K6" s="13" t="inlineStr">
         <is>
           <t>doc/active/248-MKT-2-same-game-articles-linking.md</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>248</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>248-MKT-3a-display-matrix</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>doc/active</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr"/>
+      <c r="E7" s="13" t="inlineStr"/>
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>248-MKT-3a: subtype × 表示先 matrix</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>user回答: マーケ拡張は後回し。</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="13" t="inlineStr">
         <is>
           <t>246後</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K7" s="13" t="inlineStr">
         <is>
           <t>doc/active/248-MKT-3a-display-matrix.md</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>250-QA-1</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>doc/active</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>P0(user 手直し負担軽減、即効)</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>manager / coach / player_comment 系で quote_count=0 の本文生成を止めて review 倒し</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>??????/strict????????postgame strict?farm_result?lineup?quote?</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="13" t="inlineStr">
         <is>
           <t>???????????</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="K8" s="13" t="inlineStr">
         <is>
           <t>doc/active/250-QA-1-manager-quote-zero-review.md</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>250-QA-3</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>doc/active</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>P0(user 手直し負担軽減、即効)</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>fetcher 側 weak generated title review 倒し(PHP weak_title 同等の Python 移植 + narrow phrase list)</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>??????/strict????????postgame strict?farm_result?lineup?quote?</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="13" t="inlineStr">
         <is>
           <t>???????????</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J9" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="K9" s="13" t="inlineStr">
         <is>
           <t>doc/active/250-QA-3-fetcher-weak-title-review.md</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>254</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>254-QA</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>doc/active</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>READY</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>投手回数表記揺れ正規化 helper(`6` / `6.0` / `6回1/3` / `6.1` / `6回2/3` 統一)</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>????????????????????</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>??/?????????</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>doc/active/254-QA-starter-innings-normalization.md</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>275</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>275-QA-github-actions-tests-failed-regression-audit</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>doc/active</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>AUDIT_DONE / READY_FOR_FIX</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>P1 (P0 公開復旧 観察継続中、P0 再発時はそちら最優先)</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
         <is>
           <t>275-QA-github-actions-tests-failed-regression-audit</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>ABSORB/DONE???299</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="11" t="inlineStr">
         <is>
           <t>GitHub Actions??????????CI???299??????</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" s="11" t="inlineStr">
         <is>
           <t>CI????close??</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K11" s="11" t="inlineStr">
         <is>
           <t>doc/active/275-QA-github-actions-tests-failed-regression-audit.md</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>277</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>277-QA-title-player-name-backfill</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>doc/active</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>REVIEW_NEEDED</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>P1 (品質改善 series 1/4、最優先)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>277-QA-title-player-name-backfill</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G12" s="13" t="inlineStr">
         <is>
           <t>KEEP/??????</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="13" t="inlineStr">
         <is>
           <t>???????????????????????????????SEO???</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="13" t="inlineStr">
         <is>
           <t>????clarity-first???</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J12" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="K12" s="13" t="inlineStr">
         <is>
           <t>doc/active/277-QA-title-player-name-backfill.md</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>278</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>278-QA-rt-title-cleanup</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>doc/active</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>READY_FOR_FIX</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>P2 (品質改善 series 3/4)</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>278-QA-rt-title-cleanup</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G13" s="13" t="inlineStr">
         <is>
           <t>KEEP/??????</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="13" t="inlineStr">
         <is>
           <t>???????????????????????????????SEO???</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" s="13" t="inlineStr">
         <is>
           <t>????clarity-first???</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="J13" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="K13" s="13" t="inlineStr">
         <is>
           <t>doc/active/278-QA-rt-title-cleanup.md</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>279</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>279-QA-mail-subject-clarity</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>doc/active</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>READY_FOR_FIX</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>P1 (品質改善 series 2/4)</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t>279-QA-mail-subject-clarity</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="13" t="inlineStr">
         <is>
           <t>KEEP/??????</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" s="13" t="inlineStr">
         <is>
           <t>???????????????????????????????SEO???</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I14" s="13" t="inlineStr">
         <is>
           <t>????clarity-first???</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="J14" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="K14" s="13" t="inlineStr">
         <is>
           <t>doc/active/279-QA-mail-subject-clarity.md</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>280</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>280-QA-summary-excerpt-cleanup</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>doc/active</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>READY_FOR_FIX</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>P2 (品質改善 series 4/4)</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>280-QA-summary-excerpt-cleanup</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="13" t="inlineStr">
         <is>
           <t>KEEP/??????</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" s="13" t="inlineStr">
         <is>
           <t>???????????????????????????????SEO???</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I15" s="13" t="inlineStr">
         <is>
           <t>????clarity-first???</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="J15" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="K15" s="13" t="inlineStr">
         <is>
           <t>doc/active/280-QA-summary-excerpt-cleanup.md</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>281</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>281-QA-farm-result-backlog-allowlist</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>doc/active</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>REVIEW_NEEDED</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>P1 (昼帯コンテンツ充実)</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>281-QA-farm-result-backlog-allowlist</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="13" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H16" s="13" t="inlineStr">
         <is>
           <t>??????????????????????????</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I16" s="13" t="inlineStr">
         <is>
           <t>??/?????????</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="J16" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="K16" s="13" t="inlineStr">
         <is>
           <t>doc/active/281-QA-farm-result-backlog-allowlist.md</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>282-COST-gemini-preflight-article-gate</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>doc/active</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>REVIEW_NEEDED</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>P1 (cost 削減)</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>282-COST-gemini-preflight-article-gate</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="13" t="inlineStr">
         <is>
           <t>HOLD/??</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" s="13" t="inlineStr">
         <is>
           <t>Gemini preflight gate?????flag ON??????</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" s="13" t="inlineStr">
         <is>
           <t>293 FULL_EXERCISE_OK????</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J17" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="K17" s="13" t="inlineStr">
         <is>
           <t>doc/active/282-COST-gemini-preflight-article-gate.md</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>289</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>289-OBSERVE-post-gen-validate-mail-notification</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>doc/active</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>REVIEW_NEEDED</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>**P0 equivalent**(silent skip = user 受け入れ NG)</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>289-OBSERVE-post-gen-validate-mail-notification</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="11" t="inlineStr">
         <is>
           <t>KEEP/BUG-004親候補</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" s="11" t="inlineStr">
         <is>
           <t>post_gen_validate通知・silent skip可視化。BUG-004と関連。</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I18" s="11" t="inlineStr">
         <is>
           <t>BUG-004へ関連付け</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J18" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K18" s="11" t="inlineStr">
         <is>
           <t>doc/active/289-OBSERVE-post-gen-validate-mail-notification.md</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>290</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>290-QA-weak-title-rescue-backfill</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>doc/active</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>REVIEW_NEEDED</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>P1(289 で見えた A/B 群を publish/review に戻す)</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
         <is>
           <t>290-QA-weak-title-rescue-backfill</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="G19" s="13" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H19" s="13" t="inlineStr">
         <is>
           <t>weak title rescue???????????</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" s="13" t="inlineStr">
         <is>
           <t>title clarity????</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="J19" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="K19" s="13" t="inlineStr">
         <is>
           <t>doc/active/290-QA-weak-title-rescue-backfill.md</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>293</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>293-COST-preflight-skip-visible-notification</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>doc/active</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>DESIGN_DRAFTED(実装 hold、user 判断後 impl 起票)</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>P1(282-COST flag ON 前提条件、cost 削減と silent skip 防止のバランス)</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>293-COST-preflight-skip-visible-notification</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" s="11" t="inlineStr">
         <is>
           <t>KEEP/OBSERVE</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" s="11" t="inlineStr">
         <is>
           <t>preflight skip visible???282???</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I20" s="11" t="inlineStr">
         <is>
           <t>?exercise evidence???</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="J20" s="11" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K20" s="11" t="inlineStr">
         <is>
           <t>doc/active/293-COST-preflight-skip-visible-notification.md</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>297</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>297-OPS-pause-codex-shadow-until-redesign</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>doc/active</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>READY_FOR_EXEC(user 明示 GO 済、Codex便で execute)</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>P1(現状リスク即時遮断、defensive)</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>297-OPS-pause-codex-shadow-until-redesign</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G21" s="12" t="inlineStr">
         <is>
           <t>DONE候補</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H21" s="12" t="inlineStr">
         <is>
           <t>user回答: codex-shadow-triggerは止めた。read-onlyでpause確認できればclose候補。</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I21" s="12" t="inlineStr">
         <is>
           <t>scheduler pause確認</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J21" s="12" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="K21" s="12" t="inlineStr">
         <is>
           <t>doc/active/297-OPS-pause-codex-shadow-until-redesign.md</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>095</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>095-E-wsl-cron-reboot-resilience</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>READY(現状の WSL2 systemd 設定で auto-start 期待、reboot 検証は user op)</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>P2(095-D 完了後、095 cron 安定化の補完)</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>095-E WSL cron reboot resilience</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="G22" s="13" t="inlineStr">
         <is>
           <t>HOLD/低優先</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H22" s="13" t="inlineStr">
         <is>
           <t>WSL cron resilience。GCP移行後は優先低。</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I22" s="13" t="inlineStr">
         <is>
           <t>必要時のみ</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="J22" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="K22" s="13" t="inlineStr">
         <is>
           <t>doc/waiting/095-E-wsl-cron-reboot-resilience.md</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>155</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>155-gcp-cron-migration</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>**IN_FLIGHT**(Phase 1a `88391d0` / 1b `c5adfa3` done、Phase 2 = ChatGPT phasing 168-175 chain で展開中)</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>P0.5(速報掲示板 24/7 化、PC sleep 依存解消)</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F23" s="14" t="inlineStr">
         <is>
           <t>155 gcp-cron-migration(WSL cron → Cloud Run Jobs 移行)</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G23" s="14" t="inlineStr">
         <is>
           <t>OBSOLETE候補</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="H23" s="14" t="inlineStr">
         <is>
           <t>GCP cron migrationは既に移行済みの可能性高い。</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="I23" s="14" t="inlineStr">
         <is>
           <t>現状と照合</t>
         </is>
       </c>
-      <c r="J23" s="6" t="inlineStr">
+      <c r="J23" s="14" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="K23" s="6" t="inlineStr">
+      <c r="K23" s="14" t="inlineStr">
         <is>
           <t>doc/waiting/155-gcp-cron-migration.md</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>195</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>195-article-footer-manual-x-share-corner</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>READY_FOR_AUTH_EXECUTOR</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>P0.5</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F24" s="12" t="inlineStr">
         <is>
           <t>195 article footer 手動 X 投稿シェアコーナー(B1)</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H24" s="12" t="inlineStr">
         <is>
           <t>user回答: 記事下の手動Xシェア導線は完全にはできていない。</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
+      <c r="I24" s="12" t="inlineStr">
         <is>
           <t>246/marketing laneとは別にfront確認</t>
         </is>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="J24" s="12" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="K24" s="12" t="inlineStr">
         <is>
           <t>doc/waiting/195-article-footer-manual-x-share-corner.md</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>197</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>197-195-live-deploy</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>READY_FOR_AUTH_EXECUTOR</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr">
         <is>
           <t>P0.5</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F25" s="12" t="inlineStr">
         <is>
           <t>197 / 195 article footer X share corner live deploy(canary disabled start)</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="12" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H25" s="12" t="inlineStr">
         <is>
           <t>user回答: 195が完全ではないためlive deploy/残作業確認が必要。</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="I25" s="12" t="inlineStr">
         <is>
           <t>195とセットで確認</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="J25" s="12" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="K25" s="12" t="inlineStr">
         <is>
           <t>doc/waiting/197-195-live-deploy.md</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>201-readiness-guard-test-time-dependent-flaky</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="13" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>**READY**</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>201 readiness-guard test time-dependent flaky</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="G26" s="13" t="inlineStr">
         <is>
           <t>ABSORB?299</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H26" s="13" t="inlineStr">
         <is>
           <t>pytest/flaky??????201?299???????</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I26" s="13" t="inlineStr">
         <is>
           <t>299???</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="J26" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="K26" s="13" t="inlineStr">
         <is>
           <t>doc/waiting/201-readiness-guard-test-time-dependent-flaky.md</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>205</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>205-gcp-runtime-drift-audit</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="13" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D27" s="13" t="inlineStr">
         <is>
           <t>WAITING</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>P0.5</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F27" s="13" t="inlineStr">
         <is>
           <t>205 GCP runtime drift audit</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G27" s="13" t="inlineStr">
         <is>
           <t>HOLD/ABSORB</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H27" s="13" t="inlineStr">
         <is>
           <t>runtime drift audit。230/opsへ吸収。</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I27" s="13" t="inlineStr">
         <is>
           <t>必要時</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="J27" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="K27" s="13" t="inlineStr">
         <is>
           <t>doc/waiting/205-gcp-runtime-drift-audit.md</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>210</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>210-primary-source-expansion-plan</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="13" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>REVIEW_NEEDED</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>P0.5</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F28" s="13" t="inlineStr">
         <is>
           <t>210 primary source expansion plan(doc-only spec)</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G28" s="13" t="inlineStr">
         <is>
           <t>ABSORB?288</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H28" s="13" t="inlineStr">
         <is>
           <t>source expansion??288????OK?</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I28" s="13" t="inlineStr">
         <is>
           <t>288?????????</t>
         </is>
       </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="J28" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="K28" s="13" t="inlineStr">
         <is>
           <t>doc/waiting/210-primary-source-expansion-plan.md</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>210</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>210b-rss-sources-config-additions</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="13" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t>REVIEW_NEEDED</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>P0.5</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F29" s="13" t="inlineStr">
         <is>
           <t>210b RSS source config additions(repo-only audit)</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G29" s="13" t="inlineStr">
         <is>
           <t>ABSORB?288</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H29" s="13" t="inlineStr">
         <is>
           <t>source expansion??288????OK?</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I29" s="13" t="inlineStr">
         <is>
           <t>288?????????</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="J29" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="K29" s="13" t="inlineStr">
         <is>
           <t>doc/waiting/210b-rss-sources-config-additions.md</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>210</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>210e-youtube-video-source-coverage-audit</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="13" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>REVIEW_NEEDED</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F30" s="13" t="inlineStr">
         <is>
           <t>210e YouTube / 公式動画 source coverage audit</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G30" s="13" t="inlineStr">
         <is>
           <t>ABSORB?288</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="H30" s="13" t="inlineStr">
         <is>
           <t>source expansion??288????OK?</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I30" s="13" t="inlineStr">
         <is>
           <t>288?????????</t>
         </is>
       </c>
-      <c r="J30" s="5" t="inlineStr">
+      <c r="J30" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="K30" s="13" t="inlineStr">
         <is>
           <t>doc/waiting/210e-youtube-video-source-coverage-audit.md</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>230-gcp-cost-governor-and-runtime-spend-reduction</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" s="13" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>REVIEW_NEEDED</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>P0.5</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F31" s="13" t="inlineStr">
         <is>
           <t>230 GCP cost governor + runtime spend reduction</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G31" s="13" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="H31" s="13" t="inlineStr">
         <is>
           <t>GCP runtime cost????????????????</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="I31" s="13" t="inlineStr">
         <is>
           <t>???</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="J31" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="K31" s="13" t="inlineStr">
         <is>
           <t>doc/waiting/230-gcp-cost-governor-and-runtime-spend-reduction.md</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
         <is>
           <t>230A-gcp-runtime-cost-governor-plan</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="13" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D32" s="13" t="inlineStr">
         <is>
           <t>REVIEW_NEEDED</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="E32" s="13" t="inlineStr">
         <is>
           <t>P0.5</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F32" s="13" t="inlineStr">
         <is>
           <t>230-A GCP runtime cost governor 具体提案</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="G32" s="13" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="H32" s="13" t="inlineStr">
         <is>
           <t>GCP runtime cost????????????????</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I32" s="13" t="inlineStr">
         <is>
           <t>???</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr">
+      <c r="J32" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="K32" s="13" t="inlineStr">
         <is>
           <t>doc/waiting/230A-gcp-runtime-cost-governor-plan.md</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="13" t="inlineStr">
         <is>
           <t>230A1-scheduler-cadence-phase1-runbook</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" s="13" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D33" s="13" t="inlineStr">
         <is>
           <t>REVIEW_NEEDED</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>P0.5</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F33" s="13" t="inlineStr">
         <is>
           <t>230-A1 scheduler cadence governor phase 1 runbook</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G33" s="13" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="H33" s="13" t="inlineStr">
         <is>
           <t>GCP runtime cost????????????????</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I33" s="13" t="inlineStr">
         <is>
           <t>???</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="J33" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="K33" s="13" t="inlineStr">
         <is>
           <t>doc/waiting/230A1-scheduler-cadence-phase1-runbook.md</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>230D-scheduler-overlap-audit</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="13" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>REVIEW_NEEDED</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
         <is>
           <t>P0.5</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F34" s="13" t="inlineStr">
         <is>
           <t>230-D scheduler overlap audit</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G34" s="13" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="H34" s="13" t="inlineStr">
         <is>
           <t>GCP runtime cost????????????????</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="I34" s="13" t="inlineStr">
         <is>
           <t>???</t>
         </is>
       </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="J34" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="K34" s="13" t="inlineStr">
         <is>
           <t>doc/waiting/230D-scheduler-overlap-audit.md</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>234</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>234-impl-7</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="11" t="inlineStr">
         <is>
           <t>READY_FOR_AUTH_EXECUTOR</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E35" s="11" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F35" s="11" t="inlineStr">
         <is>
           <t>234 contract 反映(probable_starter / pregame の本文 hardening)</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G35" s="11" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="H35" s="11" t="inlineStr">
         <is>
           <t>??????/strict????????postgame strict?farm_result?lineup?quote?</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="I35" s="11" t="inlineStr">
         <is>
           <t>???????????</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr">
+      <c r="J35" s="11" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K35" s="3" t="inlineStr">
+      <c r="K35" s="11" t="inlineStr">
         <is>
           <t>doc/waiting/234-impl-7-probable-starter-pregame-body-hardening.md</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>238</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>238-night-draft-only-and-morning-decision-report</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" s="13" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" s="13" t="inlineStr">
         <is>
           <t>WAITING</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>P0.5</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F36" s="13" t="inlineStr">
         <is>
           <t>238 night-draft-only mode + morning decision report</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G36" s="13" t="inlineStr">
         <is>
           <t>OBSOLETE??</t>
         </is>
       </c>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="H36" s="13" t="inlineStr">
         <is>
           <t>??draft-only / ??????????</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="I36" s="13" t="inlineStr">
         <is>
           <t>obsolete??</t>
         </is>
       </c>
-      <c r="J36" s="5" t="inlineStr">
+      <c r="J36" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K36" s="5" t="inlineStr">
+      <c r="K36" s="13" t="inlineStr">
         <is>
           <t>doc/waiting/238-night-draft-only-and-morning-decision-report.md</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>246</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" s="13" t="inlineStr">
         <is>
           <t>246-MKT-today-giants-fan-guide</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" s="13" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" s="13" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E37" s="13" t="inlineStr">
         <is>
           <t>P0.5</t>
         </is>
       </c>
-      <c r="F37" s="5" t="inlineStr">
+      <c r="F37" s="13" t="inlineStr">
         <is>
           <t>246-MKT today giants fan guide</t>
         </is>
       </c>
-      <c r="G37" s="5" t="inlineStr">
+      <c r="G37" s="13" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="H37" s="13" t="inlineStr">
         <is>
           <t>user回答: 今日の巨人ファン観戦ガイドはやりたい。</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="I37" s="13" t="inlineStr">
         <is>
           <t>MKT本線として保持</t>
         </is>
       </c>
-      <c r="J37" s="5" t="inlineStr">
+      <c r="J37" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="K37" s="13" t="inlineStr">
         <is>
           <t>doc/waiting/246-MKT-today-giants-fan-guide.md</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>249</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="13" t="inlineStr">
         <is>
           <t>249-INGEST-live-game-ingestion-expansion</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="13" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr">
+      <c r="D38" s="13" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="E38" s="13" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="F38" s="13" t="inlineStr">
         <is>
           <t>249-INGEST live game ingestion expansion</t>
         </is>
       </c>
-      <c r="G38" s="5" t="inlineStr">
+      <c r="G38" s="13" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="H38" s="13" t="inlineStr">
         <is>
           <t>試合中ingestion強化。Cloud Run/Scheduler影響大。</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="I38" s="13" t="inlineStr">
         <is>
           <t>user GOまで保持</t>
         </is>
       </c>
-      <c r="J38" s="5" t="inlineStr">
+      <c r="J38" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="K38" s="13" t="inlineStr">
         <is>
           <t>doc/waiting/249-INGEST-live-game-ingestion-expansion.md</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>251</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="13" t="inlineStr">
         <is>
           <t>251-SEO</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C39" s="13" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D39" s="13" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E39" s="13" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F39" s="13" t="inlineStr">
         <is>
           <t>default noindex からの部分 index 解放戦略(後段相談、HOLD)</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G39" s="13" t="inlineStr">
         <is>
           <t>DONE/OBSOLETE候補</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="H39" s="13" t="inlineStr">
         <is>
           <t>user回答: SEOはいじらない、もうできている。</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I39" s="13" t="inlineStr">
         <is>
           <t>ACTIVEに上げない</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr">
+      <c r="J39" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="K39" s="13" t="inlineStr">
         <is>
           <t>doc/waiting/251-SEO-noindex-release-strategy.md</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="A40" s="14" t="inlineStr">
         <is>
           <t>252</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B40" s="14" t="inlineStr">
         <is>
           <t>252-QA</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="14" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D40" s="14" t="inlineStr">
         <is>
           <t>BACKLOG</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="E40" s="14" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr">
+      <c r="F40" s="14" t="inlineStr">
         <is>
           <t>X 投稿候補 path 単独 fact check 追加(現状 publish_notice_email_sender 経由のみ、x_post_generator 単独経路の薄い穴を埋める narrow)</t>
         </is>
       </c>
-      <c r="G40" s="6" t="inlineStr">
+      <c r="G40" s="14" t="inlineStr">
         <is>
           <t>OBSOLETE候補</t>
         </is>
       </c>
-      <c r="H40" s="6" t="inlineStr">
+      <c r="H40" s="14" t="inlineStr">
         <is>
           <t>user回答: 不要。XはGPTs手動運用へ寄せたため優先度低。</t>
         </is>
       </c>
-      <c r="I40" s="6" t="inlineStr">
+      <c r="I40" s="14" t="inlineStr">
         <is>
           <t>obsolete候補へ</t>
         </is>
       </c>
-      <c r="J40" s="6" t="inlineStr">
+      <c r="J40" s="14" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K40" s="6" t="inlineStr">
+      <c r="K40" s="14" t="inlineStr">
         <is>
           <t>doc/waiting/252-QA-X-fact-check-backlog.md</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="13" t="inlineStr">
         <is>
           <t>253</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" s="13" t="inlineStr">
         <is>
           <t>253-QA</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C41" s="13" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D41" s="13" t="inlineStr">
         <is>
           <t>NOT_NOW</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E41" s="13" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F41" s="13" t="inlineStr">
         <is>
           <t>mail summary 内 source 断片の fact contains check(現状 truncation のみ、実例待ち)</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G41" s="13" t="inlineStr">
         <is>
           <t>HOLD/低優先</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="H41" s="13" t="inlineStr">
         <is>
           <t>mail summary fact checkは通知本文品質。P3。</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="I41" s="13" t="inlineStr">
         <is>
           <t>必要時だけ</t>
         </is>
       </c>
-      <c r="J41" s="5" t="inlineStr">
+      <c r="J41" s="13" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="K41" s="5" t="inlineStr">
+      <c r="K41" s="13" t="inlineStr">
         <is>
           <t>doc/waiting/253-QA-mail-summary-fact-check-backlog.md</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="13" t="inlineStr">
         <is>
           <t>255</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B42" s="13" t="inlineStr">
         <is>
           <t>255-MKT-fan-guide-expansion-and-comment-badge</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C42" s="13" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
+      <c r="D42" s="13" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="E42" s="13" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F42" s="5" t="inlineStr">
+      <c r="F42" s="13" t="inlineStr">
         <is>
           <t>255-MKT fan guide expansion and comment badge</t>
         </is>
       </c>
-      <c r="G42" s="5" t="inlineStr">
+      <c r="G42" s="13" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr">
+      <c r="H42" s="13" t="inlineStr">
         <is>
           <t>user回答: コメントbadge等は後回し。</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="I42" s="13" t="inlineStr">
         <is>
           <t>246後</t>
         </is>
       </c>
-      <c r="J42" s="5" t="inlineStr">
+      <c r="J42" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K42" s="5" t="inlineStr">
+      <c r="K42" s="13" t="inlineStr">
         <is>
           <t>doc/waiting/255-MKT-fan-guide-expansion-and-comment-badge.md</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="13" t="inlineStr">
         <is>
           <t>256</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" s="13" t="inlineStr">
         <is>
           <t>256-QA-manager-player-quote-strict-subset</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C43" s="13" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D43" s="13" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="E43" s="13" t="inlineStr">
         <is>
           <t>P0.5</t>
         </is>
       </c>
-      <c r="F43" s="5" t="inlineStr">
+      <c r="F43" s="13" t="inlineStr">
         <is>
           <t>256-QA manager/player quote strict subset</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G43" s="13" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
+      <c r="H43" s="13" t="inlineStr">
         <is>
           <t>??????/strict????????postgame strict?farm_result?lineup?quote?</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="I43" s="13" t="inlineStr">
         <is>
           <t>???????????</t>
         </is>
       </c>
-      <c r="J43" s="5" t="inlineStr">
+      <c r="J43" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K43" s="5" t="inlineStr">
+      <c r="K43" s="13" t="inlineStr">
         <is>
           <t>doc/waiting/256-QA-manager-player-quote-strict-subset.md</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="13" t="inlineStr">
         <is>
           <t>260</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B44" s="13" t="inlineStr">
         <is>
           <t>260-MKT-fan-original-article-types-and-templates</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C44" s="13" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr">
+      <c r="D44" s="13" t="inlineStr">
         <is>
           <t>HOLD_DESIGN</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E44" s="13" t="inlineStr">
         <is>
           <t>P2 (design only、実装しない)</t>
         </is>
       </c>
-      <c r="F44" s="5" t="inlineStr">
+      <c r="F44" s="13" t="inlineStr">
         <is>
           <t>巨人ファン向け独自記事型・テンプレ設計</t>
         </is>
       </c>
-      <c r="G44" s="5" t="inlineStr">
+      <c r="G44" s="13" t="inlineStr">
         <is>
           <t>HOLD_DESIGN</t>
         </is>
       </c>
-      <c r="H44" s="5" t="inlineStr">
+      <c r="H44" s="13" t="inlineStr">
         <is>
           <t>user回答: 独自記事型は後回し。</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="I44" s="13" t="inlineStr">
         <is>
           <t>設計保持のみ</t>
         </is>
       </c>
-      <c r="J44" s="5" t="inlineStr">
+      <c r="J44" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K44" s="5" t="inlineStr">
+      <c r="K44" s="13" t="inlineStr">
         <is>
           <t>doc/waiting/260-MKT-fan-original-article-types-and-templates.md</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="13" t="inlineStr">
         <is>
           <t>264</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B45" s="13" t="inlineStr">
         <is>
           <t>264-QA-cleanup-existing-duplicates</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" s="13" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D45" s="13" t="inlineStr">
         <is>
           <t>DESIGN_DRAFTED + HOLD(cleanup mutation HOLD)</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="E45" s="13" t="inlineStr">
         <is>
           <t>**P2**(read-only audit のみ即可、cleanup mutation は user 明示 GO 必須)</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F45" s="13" t="inlineStr">
         <is>
           <t>264-QA-cleanup-existing-duplicates</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
+      <c r="G45" s="13" t="inlineStr">
         <is>
           <t>ABSORB/??????</t>
         </is>
       </c>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="H45" s="13" t="inlineStr">
         <is>
           <t>??cleanup?????????????????</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="I45" s="13" t="inlineStr">
         <is>
           <t>229/235/300/BUG-004???</t>
         </is>
       </c>
-      <c r="J45" s="5" t="inlineStr">
+      <c r="J45" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="K45" s="13" t="inlineStr">
         <is>
           <t>doc/waiting/264-QA-cleanup-existing-duplicates.md</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
+      <c r="A46" s="14" t="inlineStr">
         <is>
           <t>274</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B46" s="14" t="inlineStr">
         <is>
           <t>274-OPS-mail-filter-github-actions-noise</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C46" s="14" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D46" s="14" t="inlineStr">
         <is>
           <t>READY_FOR_USER_APPLY</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E46" s="14" t="inlineStr">
         <is>
           <t>P2 (受信トレイ整理、本番影響なし)</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
+      <c r="F46" s="14" t="inlineStr">
         <is>
           <t>274-OPS-mail-filter-github-actions-noise</t>
         </is>
       </c>
-      <c r="G46" s="6" t="inlineStr">
+      <c r="G46" s="14" t="inlineStr">
         <is>
           <t>OBSOLETE候補</t>
         </is>
       </c>
-      <c r="H46" s="6" t="inlineStr">
+      <c r="H46" s="14" t="inlineStr">
         <is>
           <t>user回答: 不要。GmailフィルタでありCI赤の根本対応ではない。</t>
         </is>
       </c>
-      <c r="I46" s="6" t="inlineStr">
+      <c r="I46" s="14" t="inlineStr">
         <is>
           <t>obsolete候補へ</t>
         </is>
       </c>
-      <c r="J46" s="6" t="inlineStr">
+      <c r="J46" s="14" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K46" s="6" t="inlineStr">
+      <c r="K46" s="14" t="inlineStr">
         <is>
           <t>doc/waiting/274-OPS-mail-filter-github-actions-noise.md</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="13" t="inlineStr">
         <is>
           <t>283</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B47" s="13" t="inlineStr">
         <is>
           <t>283-MKT-unique-article-requirements-and-regression-contract</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" s="13" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D47" s="13" t="inlineStr">
         <is>
           <t>DESIGN_ONLY (実装なし、要件定義のみ)</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E47" s="13" t="inlineStr">
         <is>
           <t>P1 (個性的記事の土台、既存テンプレ崩さず定義)</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F47" s="13" t="inlineStr">
         <is>
           <t>283-MKT-unique-article-requirements-and-regression-contract</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="G47" s="13" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="H47" s="5" t="inlineStr">
+      <c r="H47" s="13" t="inlineStr">
         <is>
           <t>??????/regression contract????</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="I47" s="13" t="inlineStr">
         <is>
           <t>??/???????</t>
         </is>
       </c>
-      <c r="J47" s="5" t="inlineStr">
+      <c r="J47" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="K47" s="13" t="inlineStr">
         <is>
           <t>doc/waiting/283-MKT-unique-article-requirements-and-regression-contract.md</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" s="13" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B48" s="13" t="inlineStr">
         <is>
           <t>288-INGEST-source-coverage-expansion</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C48" s="13" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D48" s="13" t="inlineStr">
         <is>
           <t>DESIGN_DRAFTED + HOLD</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E48" s="13" t="inlineStr">
         <is>
           <t>P2(289 安定後、source 拡張)</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F48" s="13" t="inlineStr">
         <is>
           <t>288-INGEST-source-coverage-expansion</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr">
+      <c r="G48" s="13" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="H48" s="13" t="inlineStr">
         <is>
           <t>user回答: source追加・取得元拡張は後で。</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="I48" s="13" t="inlineStr">
         <is>
           <t>source追加はuser GOまでHOLD</t>
         </is>
       </c>
-      <c r="J48" s="5" t="inlineStr">
+      <c r="J48" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K48" s="5" t="inlineStr">
+      <c r="K48" s="13" t="inlineStr">
         <is>
           <t>doc/waiting/288-INGEST-source-coverage-expansion.md</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
+      <c r="A49" s="13" t="inlineStr">
         <is>
           <t>291</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B49" s="13" t="inlineStr">
         <is>
           <t>291-OBSERVE-candidate-terminal-outcome-contract</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C49" s="13" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D49" s="13" t="inlineStr">
         <is>
           <t>DESIGN_DRAFTED(実装 hold、289 完遂後 user 判断)</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E49" s="13" t="inlineStr">
         <is>
           <t>P0 equivalent(silent skip 再発防止の契約)</t>
         </is>
       </c>
-      <c r="F49" s="5" t="inlineStr">
+      <c r="F49" s="13" t="inlineStr">
         <is>
           <t>291-OBSERVE-candidate-terminal-outcome-contract</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G49" s="13" t="inlineStr">
         <is>
           <t>ACTIVE??/BUG-004+</t>
         </is>
       </c>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="H49" s="13" t="inlineStr">
         <is>
           <t>???=publish?????publishable??OK???????review/hold/????????????????</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="I49" s="13" t="inlineStr">
         <is>
           <t>BUG-004?????read-only audit</t>
         </is>
       </c>
-      <c r="J49" s="5" t="inlineStr">
+      <c r="J49" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K49" s="5" t="inlineStr">
+      <c r="K49" s="13" t="inlineStr">
         <is>
           <t>doc/waiting/291-OBSERVE-candidate-terminal-outcome-contract.md</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="13" t="inlineStr">
         <is>
           <t>292</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B50" s="13" t="inlineStr">
         <is>
           <t>292-OBSERVE-body-contract-fail-notification</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C50" s="13" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
+      <c r="D50" s="13" t="inlineStr">
         <is>
           <t>DESIGN_DRAFTED(実装 hold、289 完遂後 user 判断)</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="E50" s="13" t="inlineStr">
         <is>
           <t>P0 equivalent(silent skip 第 2 経路)</t>
         </is>
       </c>
-      <c r="F50" s="5" t="inlineStr">
+      <c r="F50" s="13" t="inlineStr">
         <is>
           <t>292-OBSERVE-body-contract-fail-notification</t>
         </is>
       </c>
-      <c r="G50" s="5" t="inlineStr">
+      <c r="G50" s="13" t="inlineStr">
         <is>
           <t>ABSORB/ledger-only</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="H50" s="13" t="inlineStr">
         <is>
           <t>body_contract fail?????????ledger/log????????????</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="I50" s="13" t="inlineStr">
         <is>
           <t>BUG-004???????????????</t>
         </is>
       </c>
-      <c r="J50" s="5" t="inlineStr">
+      <c r="J50" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K50" s="5" t="inlineStr">
+      <c r="K50" s="13" t="inlineStr">
         <is>
           <t>doc/waiting/292-OBSERVE-body-contract-fail-notification.md</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" s="11" t="inlineStr">
         <is>
           <t>294</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t>294-PROCESS-release-composition-gate</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C51" s="11" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D51" s="11" t="inlineStr">
         <is>
           <t>DESIGN_DRAFTED</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E51" s="11" t="inlineStr">
         <is>
           <t>P1(release management、HOLD ticket 暗黙 carry 再発防止)</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t>294-PROCESS-release-composition-gate</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="G51" s="11" t="inlineStr">
         <is>
           <t>KEEP/親ticket</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="H51" s="11" t="inlineStr">
         <is>
           <t>release composition gate。BUG-005/006/007/009の吸収先。</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr">
+      <c r="I51" s="11" t="inlineStr">
         <is>
           <t>統合親にする</t>
         </is>
       </c>
-      <c r="J51" s="3" t="inlineStr">
+      <c r="J51" s="11" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="K51" s="3" t="inlineStr">
+      <c r="K51" s="11" t="inlineStr">
         <is>
           <t>doc/waiting/294-PROCESS-release-composition-gate.md</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="A52" s="13" t="inlineStr">
         <is>
           <t>295</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B52" s="13" t="inlineStr">
         <is>
           <t>295-QA-subtype-evaluator-misclassify-fix</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C52" s="13" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D52" s="13" t="inlineStr">
         <is>
           <t>DESIGN_DRAFTED + HOLD(289 安定 + 290 整理後 user 判断)</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E52" s="13" t="inlineStr">
         <is>
           <t>P1(silent 候補消失の主因の 1 つ、2-3 件/trigger)</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F52" s="13" t="inlineStr">
         <is>
           <t>295-QA-subtype-evaluator-misclassify-fix</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="G52" s="13" t="inlineStr">
         <is>
           <t>KEEP/P1??</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="H52" s="13" t="inlineStr">
         <is>
           <t>subtype??????????????????comment??postgame???????????????????fact????</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="I52" s="13" t="inlineStr">
         <is>
           <t>295???234/247?????guard??</t>
         </is>
       </c>
-      <c r="J52" s="5" t="inlineStr">
+      <c r="J52" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K52" s="5" t="inlineStr">
+      <c r="K52" s="13" t="inlineStr">
         <is>
           <t>doc/waiting/295-QA-subtype-evaluator-misclassify-fix.md</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="A53" s="13" t="inlineStr">
         <is>
           <t>296</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B53" s="13" t="inlineStr">
         <is>
           <t>296-OBSERVE-codex-shadow-role-redesign</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C53" s="13" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D53" s="13" t="inlineStr">
         <is>
           <t>DESIGN_DRAFTED + HOLD</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E53" s="13" t="inlineStr">
         <is>
           <t>P1(GCP Codex 役割明確化、現状観察不能で危険)</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="F53" s="13" t="inlineStr">
         <is>
           <t>296-OBSERVE-codex-shadow-role-redesign</t>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="G53" s="13" t="inlineStr">
         <is>
           <t>OBSOLETE候補</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="H53" s="13" t="inlineStr">
         <is>
           <t>user回答: codex-shadow再設計はいらない。</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="I53" s="13" t="inlineStr">
         <is>
           <t>297 pause確認後、再設計はobsolete候補</t>
         </is>
       </c>
-      <c r="J53" s="5" t="inlineStr">
+      <c r="J53" s="13" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K53" s="5" t="inlineStr">
+      <c r="K53" s="13" t="inlineStr">
         <is>
           <t>doc/waiting/296-OBSERVE-codex-shadow-role-redesign.md</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr"/>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="A54" s="10" t="inlineStr"/>
+      <c r="B54" s="10" t="inlineStr">
         <is>
           <t>HALLUC-LANE-002-llm-based-fact-check-augmentation</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C54" s="10" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D54" s="10" t="inlineStr">
         <is>
           <t>**doc-first 起票のみ**(実装 fire は user 明示 trigger 後、Gemini API 課金 = CLAUDE.md §11 user judgment 8 類型該当)</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E54" s="10" t="inlineStr">
         <is>
           <t>P1(PUB-004 安定運用後の品質強化レーン、PUB-004 の前提**ではない**)</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F54" s="10" t="inlineStr">
         <is>
           <t>HALLUC-LANE-002 LLM-based fact-check augmentation</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G54" s="10" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H54" s="10" t="inlineStr">
         <is>
           <t>個別確認が必要。</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="I54" s="10" t="inlineStr">
         <is>
           <t>棚卸し継続</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="J54" s="10" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
+      <c r="K54" s="10" t="inlineStr">
         <is>
           <t>doc/waiting/HALLUC-LANE-002-llm-based-fact-check-augmentation.md</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr"/>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="A55" s="10" t="inlineStr"/>
+      <c r="B55" s="10" t="inlineStr">
         <is>
           <t>PUB-004-D-all-eligible-draft-backlog-publish-ramp</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C55" s="10" t="inlineStr">
         <is>
           <t>doc/waiting</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D55" s="10" t="inlineStr">
         <is>
           <t>READY(PUB-004-B `f451f17` land 後の主線)</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E55" s="10" t="inlineStr">
         <is>
           <t>**P0.5**</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F55" s="10" t="inlineStr">
         <is>
           <t>PUB-004-D all-eligible-draft-backlog-publish-ramp</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G55" s="10" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H55" s="10" t="inlineStr">
         <is>
           <t>個別確認が必要。</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>棚卸し継続</t>
         </is>
       </c>
-      <c r="J55" s="2" t="inlineStr">
+      <c r="J55" s="10" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr">
+      <c r="K55" s="10" t="inlineStr">
         <is>
           <t>doc/waiting/PUB-004-D-all-eligible-draft-backlog-publish-ramp.md</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>299</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="10" t="inlineStr">
         <is>
           <t>299-QA-flaky-transient-baseline</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="10" t="inlineStr">
         <is>
           <t>docs/ops</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="10" t="inlineStr">
         <is>
           <t>OBSERVE</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E56" s="10" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" s="10" t="inlineStr">
         <is>
           <t>flaky/transient/pytest baseline??</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G56" s="10" t="inlineStr">
         <is>
           <t>KEEP?</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H56" s="10" t="inlineStr">
         <is>
           <t>pytest/CI/flaky??????201/275???????</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I56" s="10" t="inlineStr">
         <is>
           <t>CI baseline?????close?????</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="J56" s="10" t="inlineStr">
         <is>
           <t>ANSWERED</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="K56" s="10" t="inlineStr">
         <is>
           <t>docs/ops/OPS_BOARD.yaml</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/ops/チケット棚卸し案_2026-05-02.xlsx
+++ b/docs/ops/チケット棚卸し案_2026-05-02.xlsx
@@ -26,14 +26,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Hearing_Round6_Final" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Cost_Principle" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Publish0_NarrowUnlock" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_2026_05_03_PMO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'00_Final_JP'!$A$1:$C$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_ACTIVE_Detail'!$A$1:$H$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_ACTIVE_Detail'!$A$1:$H$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_KEEP_Detail'!$A$1:$E$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'03_HOLD_OBSOLETE'!$A$1:$D$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'04_Rules_Detail'!$A$1:$B$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_Claude_Prompt'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05_Claude_Prompt'!$A$1:$B$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'06_NewCandidate_GCP_Codex'!$A$1:$B$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'00_UserReview'!$A$1:$C$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'01_AllTickets'!$A$1:$K$56</definedName>
@@ -47,6 +48,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'09_Hearing_Round6_Final'!$A$1:$C$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'10_Cost_Principle'!$A$1:$B$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'07_Publish0_NarrowUnlock'!$A$1:$B$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'08_2026_05_03_PMO'!$A$1:$B$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -542,7 +544,7 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1751,7 +1753,7 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2008,8 +2010,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2130,7 +2132,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2233,7 +2235,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2332,17 +2334,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2353,168 +2355,337 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>チケット名</t>
+          <t>?????</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
         <is>
-          <t>優先度</t>
+          <t>???</t>
         </is>
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>扱い</t>
+          <t>??</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>なぜ重要か</t>
+          <t>?????</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>次にやること</t>
+          <t>??????</t>
         </is>
       </c>
       <c r="G1" s="9" t="inlineStr">
         <is>
-          <t>close条件</t>
+          <t>close??</t>
         </is>
       </c>
       <c r="H1" s="9" t="inlineStr">
         <is>
-          <t>禁止/注意</t>
+          <t>??/??</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>BUG-003</t>
+          <t>BUG-004+291</t>
         </is>
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>WP status mutation audit</t>
+          <t>publish=0???? + narrow publish-path unlock</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
         <is>
-          <t>P1候補</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>ACTIVE候補 1</t>
+          <t>ACTIVE 1???</t>
         </is>
       </c>
       <c r="E2" s="10" t="inlineStr">
         <is>
-          <t>公開状態が勝手に変わった疑い。publish済み記事がdraft/private/pending等に戻る事故があると、サイトの公開復旧・信頼性に直結する。</t>
+          <t>???????????user??????????????????????????????????publish path?????????</t>
         </is>
       </c>
       <c r="F2" s="10" t="inlineStr">
         <is>
-          <t>直近24〜72hのWP status変化、WP REST更新ログ、guarded-publish/publish-notice周辺のstatus更新pathをread-onlyで確認する。既存publishをdraft/privateへ戻す処理が存在しない、または十分guardされていることを確認する。</t>
+          <t>read-only?publish=0??????277/289/290/4-tier/duplicate/backlog/freshness/body_contract/subtype/numeric/placeholder/source facts?????????unlock??????????????292 body_contract_fail durable ledger?????????</t>
         </is>
       </c>
       <c r="G2" s="10" t="inlineStr">
         <is>
-          <t>問題なしを証拠付きで確認できた、または原因を特定して修正・verifyできた場合のみDONE。証拠なしはDONE禁止でP1_REVIEWまたはOBSERVE継続。</t>
+          <t>?????(YOSHILOVER???source_url?subtype/template_key high confidence?numeric/body pass?placeholder???silent skip???title???review/hold????)????????publish????????????body_contract_fail???????????ledger/log?????</t>
         </is>
       </c>
       <c r="H2" s="10" t="inlineStr">
         <is>
-          <t>本番変更なし。deploy/env/flag/Scheduler/SEO/source/Gemini/mail変更禁止。</t>
+          <t>publish gate?????postgame strict/stale/duplicate??????noindex???review threshold?????mail?????ticket???292??ACTIVE?????</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>BUG-004 + 291</t>
+          <t>282-COST</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>silent skip / ???? / YOSHILOVER?????? / ???????? / publish=0????</t>
+          <t>flag ON? preflight active rejection??</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>P1候補</t>
+          <t>OBSERVE</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>ACTIVE候補 2</t>
+          <t>OBSERVE</t>
         </is>
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <t>??????????publish/review/hold/skip/error??????????????YOSHILOVER???source??????????publish=0??????user?????????????????????????</t>
+          <t>282?flag ON???????????????????????????</t>
         </is>
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>????????read-only??????publish=0???277 title quality?289 post_gen_validate?290 weak title rescue???4-tier strict?duplicate/backlog/freshness?body_contract?subtype????numeric guard?placeholder?source facts??????????????????????????????publish path???narrow unlock??????</t>
+          <t>preflight active rejection?????silent skip?Gemini??mail storm?????</t>
         </is>
       </c>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <t>??run?unaccounted candidate?0?skip/hold/review???log/ledger/state row????YOSHILOVER????????????????(YOSHILOVER???source_url?subtype/template_key high confidence?numeric/body pass?placeholder???title???review/hold????)????????publish???????????DONE???</t>
+          <t>?????????????????????????</t>
         </is>
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>publish gate??????????noindex???review threshold???????mail??????292 body_contract fail?????????ledger/log????????????</t>
+          <t>?????env remove?user?????????</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>NEW_CANDIDATE</t>
+          <t>298-Phase3</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>GCP Codex WP本文修正プレビュー v0</t>
+          <t>5/3 19:35 JST 24h gate??</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>P1候補/次ACTIVE候補</t>
+          <t>OBSERVE</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>まだACTIVEではないが早めにやりたい</t>
+          <t>OBSERVE</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>本文品質を早く見たい。preview-onlyならデグレリスクを抑えてGCP Codexの実力を確認できる。</t>
+          <t>24h gate?PASS/FAIL??????</t>
         </is>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>postgameまたはfarm_result少数で、元本文と修正文候補を比較できるartifactを出す。</t>
+          <t>5/3 19:35 JST????</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>WP本文変更なし、publish変更なし、Gemini原則0で品質確認できる。</t>
+          <t>PASS/FAIL/rollback???????</t>
         </is>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
-          <t>本番本文を書き換えない。自由作文させない。</t>
+          <t>????????????</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>WP plugin upload</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>USER_DECISION_REQUIRED</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>user????</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>WP admin upload?????????????user???</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>upload????OK/HOLD/REJECT????</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>user?OK?????????</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>publish=0?????????</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H4"/>
+  <autoFilter ref="A1:H5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>BUG-004+291 publish=0???? + narrow publish-path unlock ?1??292 body_contract_fail durable ledger????????????????</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>OBSERVE</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>282-COST flag ON??preflight active rejection?? / 298 5/3 19:35 JST 24h gate??????????</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>USER_DECISION_REQUIRED</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>245 WP plugin upload???</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>277/279/278/280 title/mail/summary??234/247/250/256/254/295 ???????subtype??246-MKT/195/197/281 ????????????230/288/251/252/274/296/238 HOLD/OBSOLETE???</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>??????????????????292??ACTIVE??publish gate?????postgame strict/stale/duplicate??????noindex???review threshold?????mail???body_contract_fail??????????</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>??</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>????????????????publish path????</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>publish????</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>YOSHILOVER???source_url???subtype/template_key high confidence?numeric guard pass?body_contract pass?placeholder???silent skip???title???????????????review/hold?????</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>??Claude????</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>??Claude?BUG-004+291????????????publish=0????+narrow publish-path unlock?BUG-004+291???????????????????292 body_contract_fail durable ledger?????ACTIVE?????????????????????????????????read-only?publish=0??????????unlock???????????????????</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2531,8 +2702,8 @@
     <col width="23" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2985,7 +3156,7 @@
     <col width="27" customWidth="1" min="1" max="1"/>
     <col width="54" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3202,7 +3373,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3349,11 +3520,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3428,8 +3599,20 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>2026-05-03 ??Claude??????</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>?????????Claude?BUG-004+291???????????????publish=0???? + narrow publish-path unlock??BUG-004+291??????????????????????292 body_contract_fail durable ledger?????ACTIVE?????BUG-004+291????????????????????????ACTIVE?BUG-004+291???OBSERVE?282-COST?298-Phase3?USER_DECISION_REQUIRED?245 WP plugin upload???publish gate?????postgame strict/stale/duplicate??????noindex???review threshold???????mail????????????body_contract_fail???????????????read-only?publish=0??????????unlock???????????????????</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:B7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3444,7 +3627,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3656,7 +3839,7 @@
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3879,16 +4062,16 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="55" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
     <col width="31" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="55" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
